--- a/Bharat/Dahisaralkachs/Final Acoounts 31.03.2026.xlsx
+++ b/Bharat/Dahisaralkachs/Final Acoounts 31.03.2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BHARAT\2025-2026\BCB\Bharat\Dahisaralkachs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3735204F-EE09-489E-B83B-716FD9226D32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDA98775-8BB8-4AB3-ABF3-8461AB22752E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -445,10 +445,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="166" formatCode="0.00_)"/>
-    <numFmt numFmtId="168" formatCode="&quot;Mumbai: &quot;dd&quot;th&quot;\ mmmm\,\ yyyy"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="0.00_)"/>
+    <numFmt numFmtId="166" formatCode="&quot;Mumbai: &quot;dd&quot;th&quot;\ mmmm\,\ yyyy"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -783,7 +783,7 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -796,48 +796,124 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="12" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="13" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="12" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="12" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="12" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -849,137 +925,57 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="13" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="12" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1293,566 +1289,552 @@
   <dimension ref="A1:K92"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" style="27" customWidth="1"/>
-    <col min="2" max="2" width="30.6640625" style="27" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" style="27" customWidth="1"/>
-    <col min="4" max="4" width="13.5546875" style="27" customWidth="1"/>
-    <col min="5" max="5" width="0.88671875" style="27" customWidth="1"/>
-    <col min="6" max="6" width="13.5546875" style="27" customWidth="1"/>
-    <col min="7" max="7" width="30.6640625" style="27" customWidth="1"/>
-    <col min="8" max="8" width="12.6640625" style="27" customWidth="1"/>
-    <col min="9" max="9" width="13.5546875" style="27" customWidth="1"/>
-    <col min="10" max="16384" width="9.109375" style="27"/>
+    <col min="1" max="1" width="13.5546875" style="18" customWidth="1"/>
+    <col min="2" max="2" width="30.6640625" style="18" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" style="18" customWidth="1"/>
+    <col min="4" max="4" width="13.5546875" style="18" customWidth="1"/>
+    <col min="5" max="5" width="0.88671875" style="18" customWidth="1"/>
+    <col min="6" max="6" width="13.5546875" style="18" customWidth="1"/>
+    <col min="7" max="7" width="30.6640625" style="18" customWidth="1"/>
+    <col min="8" max="8" width="12.6640625" style="18" customWidth="1"/>
+    <col min="9" max="9" width="13.5546875" style="18" customWidth="1"/>
+    <col min="10" max="16384" width="9.109375" style="18"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="19.95" customHeight="1">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="26"/>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="56"/>
     </row>
     <row r="2" spans="1:9" ht="14.4" customHeight="1">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="57" t="s">
         <v>78</v>
       </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="30"/>
+      <c r="B2" s="58"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="58"/>
+      <c r="H2" s="58"/>
+      <c r="I2" s="59"/>
     </row>
     <row r="3" spans="1:9" ht="7.95" customHeight="1">
-      <c r="A3" s="31"/>
-      <c r="B3" s="32"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
-      <c r="G3" s="32"/>
-      <c r="H3" s="32"/>
-      <c r="I3" s="33"/>
+      <c r="A3" s="20"/>
+      <c r="I3" s="21"/>
     </row>
     <row r="4" spans="1:9" ht="16.8" customHeight="1">
-      <c r="A4" s="34" t="s">
+      <c r="A4" s="69" t="s">
         <v>102</v>
       </c>
-      <c r="B4" s="35"/>
-      <c r="C4" s="35"/>
-      <c r="D4" s="35"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="35"/>
-      <c r="H4" s="35"/>
-      <c r="I4" s="36"/>
+      <c r="B4" s="70"/>
+      <c r="C4" s="70"/>
+      <c r="D4" s="70"/>
+      <c r="E4" s="70"/>
+      <c r="F4" s="70"/>
+      <c r="G4" s="70"/>
+      <c r="H4" s="70"/>
+      <c r="I4" s="71"/>
     </row>
     <row r="5" spans="1:9" ht="7.95" customHeight="1">
-      <c r="A5" s="37"/>
-      <c r="B5" s="38"/>
-      <c r="C5" s="38"/>
-      <c r="D5" s="38"/>
-      <c r="E5" s="38"/>
-      <c r="F5" s="38"/>
-      <c r="G5" s="38"/>
-      <c r="H5" s="38"/>
-      <c r="I5" s="39"/>
+      <c r="A5" s="22"/>
+      <c r="B5" s="23"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="23"/>
+      <c r="H5" s="23"/>
+      <c r="I5" s="24"/>
     </row>
     <row r="6" spans="1:9" ht="13.8" thickBot="1">
-      <c r="A6" s="40" t="s">
+      <c r="A6" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="40" t="s">
+      <c r="B6" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="41" t="s">
+      <c r="C6" s="26" t="s">
         <v>103</v>
       </c>
-      <c r="D6" s="41" t="s">
+      <c r="D6" s="26" t="s">
         <v>103</v>
       </c>
-      <c r="E6" s="40"/>
-      <c r="F6" s="40" t="s">
+      <c r="E6" s="25"/>
+      <c r="F6" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="G6" s="40" t="s">
+      <c r="G6" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="41" t="s">
+      <c r="H6" s="26" t="s">
         <v>103</v>
       </c>
-      <c r="I6" s="41" t="s">
+      <c r="I6" s="26" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="10.050000000000001" customHeight="1">
-      <c r="A7" s="42"/>
-      <c r="B7" s="43"/>
-      <c r="C7" s="42"/>
-      <c r="D7" s="42"/>
-      <c r="E7" s="43"/>
-      <c r="F7" s="42"/>
-      <c r="G7" s="43"/>
-      <c r="H7" s="42"/>
-      <c r="I7" s="42"/>
+      <c r="A7" s="27"/>
+      <c r="B7" s="28"/>
+      <c r="C7" s="27"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="27"/>
+      <c r="G7" s="28"/>
+      <c r="H7" s="27"/>
+      <c r="I7" s="27"/>
     </row>
     <row r="8" spans="1:9" ht="15" customHeight="1">
-      <c r="A8" s="42">
+      <c r="A8" s="27">
         <v>19500</v>
       </c>
-      <c r="B8" s="43" t="s">
+      <c r="B8" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="42"/>
-      <c r="D8" s="42">
+      <c r="C8" s="27"/>
+      <c r="D8" s="27">
         <v>20400</v>
       </c>
-      <c r="E8" s="43"/>
-      <c r="F8" s="42"/>
-      <c r="G8" s="43" t="s">
+      <c r="E8" s="28"/>
+      <c r="F8" s="27"/>
+      <c r="G8" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="H8" s="42"/>
-      <c r="I8" s="42"/>
+      <c r="H8" s="27"/>
+      <c r="I8" s="27"/>
     </row>
     <row r="9" spans="1:9" ht="15" customHeight="1">
-      <c r="A9" s="42">
+      <c r="A9" s="27">
         <v>0</v>
       </c>
-      <c r="B9" s="43" t="s">
+      <c r="B9" s="28" t="s">
         <v>99</v>
       </c>
-      <c r="C9" s="42"/>
-      <c r="D9" s="42">
+      <c r="C9" s="27"/>
+      <c r="D9" s="27">
         <v>15992</v>
       </c>
-      <c r="E9" s="43"/>
-      <c r="F9" s="42">
+      <c r="E9" s="28"/>
+      <c r="F9" s="27">
         <v>20712</v>
       </c>
-      <c r="G9" s="43" t="s">
+      <c r="G9" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="H9" s="42">
+      <c r="H9" s="27">
         <v>20712</v>
       </c>
-      <c r="I9" s="42"/>
+      <c r="I9" s="27"/>
     </row>
     <row r="10" spans="1:9" ht="15" customHeight="1">
-      <c r="A10" s="42">
+      <c r="A10" s="27">
         <v>48778</v>
       </c>
-      <c r="B10" s="43" t="s">
+      <c r="B10" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="42"/>
-      <c r="D10" s="42">
+      <c r="C10" s="27"/>
+      <c r="D10" s="27">
         <v>44540</v>
       </c>
-      <c r="E10" s="43"/>
-      <c r="F10" s="42">
+      <c r="E10" s="28"/>
+      <c r="F10" s="27">
         <v>58500</v>
       </c>
-      <c r="G10" s="43" t="s">
+      <c r="G10" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="H10" s="42">
+      <c r="H10" s="27">
         <v>58500</v>
       </c>
-      <c r="I10" s="42"/>
+      <c r="I10" s="27"/>
     </row>
     <row r="11" spans="1:9" ht="15" customHeight="1">
-      <c r="A11" s="42">
+      <c r="A11" s="27">
         <v>21430</v>
       </c>
-      <c r="B11" s="43" t="s">
+      <c r="B11" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="42"/>
-      <c r="D11" s="42">
+      <c r="C11" s="27"/>
+      <c r="D11" s="27">
         <v>22850</v>
       </c>
-      <c r="E11" s="43"/>
-      <c r="F11" s="42">
+      <c r="E11" s="28"/>
+      <c r="F11" s="27">
         <v>17750</v>
       </c>
-      <c r="G11" s="43" t="s">
+      <c r="G11" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="H11" s="42">
+      <c r="H11" s="27">
         <v>16750</v>
       </c>
-      <c r="I11" s="42"/>
+      <c r="I11" s="27"/>
     </row>
     <row r="12" spans="1:9" ht="15" customHeight="1">
-      <c r="A12" s="42">
+      <c r="A12" s="27">
         <v>1500</v>
       </c>
-      <c r="B12" s="43" t="s">
+      <c r="B12" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="42"/>
-      <c r="D12" s="42">
+      <c r="C12" s="27"/>
+      <c r="D12" s="27">
         <v>1500</v>
       </c>
-      <c r="E12" s="43"/>
-      <c r="F12" s="42">
+      <c r="E12" s="28"/>
+      <c r="F12" s="27">
         <v>26100</v>
       </c>
-      <c r="G12" s="43" t="s">
+      <c r="G12" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="H12" s="42">
+      <c r="H12" s="27">
         <v>26100</v>
       </c>
-      <c r="I12" s="42"/>
+      <c r="I12" s="27"/>
     </row>
     <row r="13" spans="1:9" ht="15" customHeight="1">
-      <c r="A13" s="42">
+      <c r="A13" s="27">
         <v>3500</v>
       </c>
-      <c r="B13" s="43" t="s">
+      <c r="B13" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="42"/>
-      <c r="D13" s="42">
+      <c r="C13" s="27"/>
+      <c r="D13" s="27">
         <v>3500</v>
       </c>
-      <c r="E13" s="43"/>
-      <c r="F13" s="42">
+      <c r="E13" s="28"/>
+      <c r="F13" s="27">
         <v>13000</v>
       </c>
-      <c r="G13" s="43" t="s">
+      <c r="G13" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="H13" s="42">
+      <c r="H13" s="27">
         <v>14550</v>
       </c>
-      <c r="I13" s="42"/>
+      <c r="I13" s="27"/>
     </row>
     <row r="14" spans="1:9" ht="15" customHeight="1">
-      <c r="A14" s="42">
+      <c r="A14" s="27">
         <v>2705</v>
       </c>
-      <c r="B14" s="43" t="s">
+      <c r="B14" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="42"/>
-      <c r="D14" s="42">
+      <c r="C14" s="27"/>
+      <c r="D14" s="27">
         <v>848</v>
       </c>
-      <c r="E14" s="43"/>
-      <c r="F14" s="42">
+      <c r="E14" s="28"/>
+      <c r="F14" s="27">
         <v>11700</v>
       </c>
-      <c r="G14" s="43" t="s">
+      <c r="G14" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="H14" s="42">
+      <c r="H14" s="27">
         <v>11700</v>
       </c>
-      <c r="I14" s="42"/>
+      <c r="I14" s="27"/>
     </row>
     <row r="15" spans="1:9" ht="15" customHeight="1">
-      <c r="A15" s="42">
+      <c r="A15" s="27">
         <v>26098</v>
       </c>
-      <c r="B15" s="43" t="s">
+      <c r="B15" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="42"/>
-      <c r="D15" s="42">
+      <c r="C15" s="27"/>
+      <c r="D15" s="27">
         <v>42148</v>
       </c>
-      <c r="E15" s="43"/>
-      <c r="F15" s="44">
+      <c r="E15" s="28"/>
+      <c r="F15" s="29">
         <v>0</v>
       </c>
-      <c r="G15" s="43" t="s">
+      <c r="G15" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="H15" s="44">
+      <c r="H15" s="29">
         <v>1000</v>
       </c>
-      <c r="I15" s="42"/>
+      <c r="I15" s="27"/>
     </row>
     <row r="16" spans="1:9" ht="15" customHeight="1">
-      <c r="A16" s="42">
+      <c r="A16" s="27">
         <v>0</v>
       </c>
-      <c r="B16" s="43" t="s">
+      <c r="B16" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="42"/>
-      <c r="D16" s="42">
+      <c r="C16" s="27"/>
+      <c r="D16" s="27">
         <v>177</v>
       </c>
-      <c r="E16" s="43"/>
-      <c r="F16" s="42">
+      <c r="E16" s="28"/>
+      <c r="F16" s="27">
         <v>60000</v>
       </c>
-      <c r="G16" s="27" t="s">
+      <c r="G16" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="H16" s="42">
+      <c r="H16" s="27">
         <v>150000</v>
       </c>
-      <c r="I16" s="43"/>
+      <c r="I16" s="28"/>
     </row>
     <row r="17" spans="1:9" ht="15" customHeight="1">
-      <c r="A17" s="42">
+      <c r="A17" s="27">
         <v>5187</v>
       </c>
-      <c r="B17" s="43" t="s">
+      <c r="B17" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="42"/>
-      <c r="D17" s="42">
+      <c r="C17" s="27"/>
+      <c r="D17" s="27">
         <v>4357</v>
       </c>
-      <c r="E17" s="43"/>
-      <c r="F17" s="45">
+      <c r="E17" s="28"/>
+      <c r="F17" s="30">
         <v>32423</v>
       </c>
-      <c r="G17" s="43" t="s">
+      <c r="G17" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="H17" s="45">
+      <c r="H17" s="30">
         <v>44782</v>
       </c>
-      <c r="I17" s="42"/>
+      <c r="I17" s="27"/>
     </row>
     <row r="18" spans="1:9" ht="15" customHeight="1">
-      <c r="A18" s="42">
+      <c r="A18" s="27">
         <v>2105</v>
       </c>
-      <c r="B18" s="43" t="s">
+      <c r="B18" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="42"/>
-      <c r="D18" s="42">
+      <c r="C18" s="27"/>
+      <c r="D18" s="27">
         <v>580</v>
       </c>
-      <c r="E18" s="43"/>
-      <c r="F18" s="42">
+      <c r="E18" s="28"/>
+      <c r="F18" s="27">
         <f>SUM(F9:F17)</f>
         <v>240185</v>
       </c>
-      <c r="G18" s="43"/>
-      <c r="H18" s="42"/>
-      <c r="I18" s="42">
+      <c r="G18" s="28"/>
+      <c r="H18" s="27"/>
+      <c r="I18" s="27">
         <f>SUM(H9:H17)</f>
         <v>344094</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="15" customHeight="1">
-      <c r="A19" s="42">
+      <c r="A19" s="27">
         <v>5000</v>
       </c>
-      <c r="B19" s="43" t="s">
+      <c r="B19" s="28" t="s">
         <v>91</v>
       </c>
-      <c r="C19" s="42"/>
-      <c r="D19" s="42">
+      <c r="C19" s="27"/>
+      <c r="D19" s="27">
         <v>0</v>
       </c>
-      <c r="E19" s="43"/>
-      <c r="F19" s="42">
+      <c r="E19" s="28"/>
+      <c r="F19" s="27">
         <v>2163</v>
       </c>
-      <c r="G19" s="43" t="s">
+      <c r="G19" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="H19" s="42"/>
-      <c r="I19" s="42">
+      <c r="H19" s="27"/>
+      <c r="I19" s="27">
         <v>3222</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="15" customHeight="1">
-      <c r="A20" s="42">
+      <c r="A20" s="27">
         <v>4077</v>
       </c>
-      <c r="B20" s="43" t="s">
+      <c r="B20" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="C20" s="42"/>
-      <c r="D20" s="42">
+      <c r="C20" s="27"/>
+      <c r="D20" s="27">
         <v>2926</v>
       </c>
-      <c r="E20" s="43"/>
-      <c r="F20" s="42">
+      <c r="E20" s="28"/>
+      <c r="F20" s="27">
         <v>52088</v>
       </c>
-      <c r="G20" s="43" t="s">
+      <c r="G20" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="H20" s="42"/>
-      <c r="I20" s="42">
+      <c r="H20" s="27"/>
+      <c r="I20" s="27">
         <v>49106</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="15" customHeight="1">
-      <c r="A21" s="42">
+      <c r="A21" s="27">
         <v>230</v>
       </c>
-      <c r="B21" s="43" t="s">
+      <c r="B21" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="C21" s="42"/>
-      <c r="D21" s="42">
+      <c r="C21" s="27"/>
+      <c r="D21" s="27">
         <v>30</v>
       </c>
-      <c r="E21" s="43"/>
-      <c r="F21" s="42"/>
-      <c r="G21" s="43"/>
-      <c r="H21" s="42"/>
-      <c r="I21" s="42"/>
+      <c r="E21" s="28"/>
+      <c r="F21" s="27"/>
+      <c r="G21" s="28"/>
+      <c r="H21" s="27"/>
+      <c r="I21" s="27"/>
     </row>
     <row r="22" spans="1:9" ht="15" customHeight="1">
-      <c r="A22" s="42">
+      <c r="A22" s="27">
         <v>826</v>
       </c>
-      <c r="B22" s="43" t="s">
+      <c r="B22" s="28" t="s">
         <v>28</v>
       </c>
-      <c r="C22" s="42"/>
-      <c r="D22" s="42">
+      <c r="C22" s="27"/>
+      <c r="D22" s="27">
         <v>826</v>
       </c>
-      <c r="E22" s="43"/>
-      <c r="F22" s="42"/>
-      <c r="G22" s="43"/>
-      <c r="H22" s="42"/>
-      <c r="I22" s="42"/>
+      <c r="E22" s="28"/>
+      <c r="F22" s="27"/>
+      <c r="G22" s="28"/>
+      <c r="H22" s="27"/>
+      <c r="I22" s="27"/>
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1">
-      <c r="A23" s="42">
+      <c r="A23" s="27">
         <v>118000</v>
       </c>
-      <c r="B23" s="43" t="s">
+      <c r="B23" s="28" t="s">
         <v>93</v>
       </c>
-      <c r="C23" s="43"/>
-      <c r="D23" s="42">
+      <c r="C23" s="28"/>
+      <c r="D23" s="27">
         <v>165000</v>
       </c>
-      <c r="E23" s="43"/>
-      <c r="F23" s="42"/>
-      <c r="G23" s="43"/>
-      <c r="H23" s="42"/>
-      <c r="I23" s="42"/>
+      <c r="E23" s="28"/>
+      <c r="F23" s="27"/>
+      <c r="G23" s="28"/>
+      <c r="H23" s="27"/>
+      <c r="I23" s="27"/>
     </row>
     <row r="24" spans="1:9" ht="15" customHeight="1">
-      <c r="A24" s="42">
+      <c r="A24" s="27">
         <v>15000</v>
       </c>
-      <c r="B24" s="43" t="s">
+      <c r="B24" s="28" t="s">
         <v>94</v>
       </c>
-      <c r="C24" s="42"/>
-      <c r="D24" s="42">
+      <c r="C24" s="27"/>
+      <c r="D24" s="27">
         <v>0</v>
       </c>
-      <c r="E24" s="43"/>
-      <c r="F24" s="42"/>
-      <c r="G24" s="43"/>
-      <c r="H24" s="42"/>
-      <c r="I24" s="42"/>
+      <c r="E24" s="28"/>
+      <c r="F24" s="27"/>
+      <c r="G24" s="28"/>
+      <c r="H24" s="27"/>
+      <c r="I24" s="27"/>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="42"/>
-      <c r="B25" s="43"/>
-      <c r="C25" s="42"/>
-      <c r="D25" s="42"/>
-      <c r="E25" s="43"/>
-      <c r="F25" s="42"/>
-      <c r="G25" s="43"/>
-      <c r="H25" s="42"/>
-      <c r="I25" s="42"/>
+      <c r="A25" s="27"/>
+      <c r="B25" s="28"/>
+      <c r="C25" s="27"/>
+      <c r="D25" s="27"/>
+      <c r="E25" s="28"/>
+      <c r="F25" s="27"/>
+      <c r="G25" s="28"/>
+      <c r="H25" s="27"/>
+      <c r="I25" s="27"/>
     </row>
     <row r="26" spans="1:9" ht="15" customHeight="1">
-      <c r="A26" s="42">
+      <c r="A26" s="27">
         <f>F28-(A8+A9+A10+A11+A12+A13+A14+A15+A16+A17+A18+A19+A20+A21+A22+A23+A24)</f>
         <v>20500</v>
       </c>
-      <c r="B26" s="43" t="s">
+      <c r="B26" s="28" t="s">
         <v>80</v>
       </c>
-      <c r="C26" s="42"/>
-      <c r="D26" s="42">
+      <c r="C26" s="27"/>
+      <c r="D26" s="27">
         <f>I28-(D8+D9+D10+D11+D12+D13+D14+D15+D16+D17+D18+D19+D20+D21+D22+D23+D24)</f>
         <v>70748</v>
       </c>
-      <c r="E26" s="43"/>
-      <c r="F26" s="42">
+      <c r="E26" s="28"/>
+      <c r="F26" s="27">
         <f>A28-(F18+F19+F20+F21+F22)</f>
         <v>0</v>
       </c>
-      <c r="G26" s="43" t="s">
+      <c r="G26" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="H26" s="42"/>
-      <c r="I26" s="42">
+      <c r="H26" s="27"/>
+      <c r="I26" s="27">
         <f>D28-(I18+I19+I20+I21+I22)</f>
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="10.050000000000001" customHeight="1">
-      <c r="A27" s="42"/>
-      <c r="B27" s="43"/>
-      <c r="C27" s="42"/>
-      <c r="D27" s="42"/>
-      <c r="E27" s="43"/>
-      <c r="F27" s="42"/>
-      <c r="G27" s="43"/>
-      <c r="H27" s="42"/>
-      <c r="I27" s="42"/>
-    </row>
-    <row r="28" spans="1:9" s="48" customFormat="1" ht="19.95" customHeight="1" thickBot="1">
-      <c r="A28" s="46">
+      <c r="A27" s="27"/>
+      <c r="B27" s="28"/>
+      <c r="C27" s="27"/>
+      <c r="D27" s="27"/>
+      <c r="E27" s="28"/>
+      <c r="F27" s="27"/>
+      <c r="G27" s="28"/>
+      <c r="H27" s="27"/>
+      <c r="I27" s="27"/>
+    </row>
+    <row r="28" spans="1:9" s="33" customFormat="1" ht="19.95" customHeight="1" thickBot="1">
+      <c r="A28" s="31">
         <f>SUM(A8:A26)</f>
         <v>294436</v>
       </c>
-      <c r="B28" s="64" t="s">
+      <c r="B28" s="41" t="s">
         <v>112</v>
       </c>
-      <c r="C28" s="46"/>
-      <c r="D28" s="46">
+      <c r="C28" s="31"/>
+      <c r="D28" s="31">
         <f>SUM(D8:D26)</f>
         <v>396422</v>
       </c>
-      <c r="E28" s="47"/>
-      <c r="F28" s="46">
+      <c r="E28" s="32"/>
+      <c r="F28" s="31">
         <f>F18+F19+F20+F21</f>
         <v>294436</v>
       </c>
-      <c r="G28" s="64" t="s">
+      <c r="G28" s="41" t="s">
         <v>112</v>
       </c>
-      <c r="H28" s="46"/>
-      <c r="I28" s="46">
+      <c r="H28" s="31"/>
+      <c r="I28" s="31">
         <f>SUM(I18:I21)</f>
         <v>396422</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="8.1" customHeight="1" thickTop="1">
-      <c r="A29" s="31"/>
-      <c r="B29" s="32"/>
-      <c r="C29" s="32"/>
-      <c r="D29" s="32"/>
-      <c r="E29" s="32"/>
-      <c r="F29" s="32"/>
-      <c r="G29" s="32"/>
-      <c r="H29" s="32"/>
-      <c r="I29" s="33"/>
+      <c r="A29" s="20"/>
+      <c r="I29" s="21"/>
     </row>
     <row r="30" spans="1:9" ht="14.4">
       <c r="A30" s="10" t="s">
@@ -1861,856 +1843,835 @@
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
       <c r="D30" s="11"/>
-      <c r="E30" s="32"/>
-      <c r="F30" s="32"/>
-      <c r="G30" s="49"/>
-      <c r="H30" s="32"/>
-      <c r="I30" s="33"/>
+      <c r="G30" s="19"/>
+      <c r="I30" s="21"/>
     </row>
     <row r="31" spans="1:9" ht="15.75" customHeight="1">
       <c r="A31" s="12"/>
-      <c r="B31" s="13"/>
-      <c r="C31" s="13"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="32"/>
-      <c r="F31" s="32"/>
-      <c r="G31" s="50" t="s">
+      <c r="B31" s="63"/>
+      <c r="C31" s="63"/>
+      <c r="D31" s="63"/>
+      <c r="G31" s="64" t="s">
         <v>110</v>
       </c>
-      <c r="H31" s="50"/>
-      <c r="I31" s="51"/>
+      <c r="H31" s="64"/>
+      <c r="I31" s="65"/>
     </row>
     <row r="32" spans="1:9" ht="14.4">
       <c r="A32" s="12"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="32"/>
-      <c r="F32" s="32"/>
-      <c r="G32" s="52"/>
-      <c r="H32" s="52"/>
-      <c r="I32" s="53"/>
+      <c r="B32" s="68"/>
+      <c r="C32" s="68"/>
+      <c r="D32" s="68"/>
+      <c r="G32" s="66"/>
+      <c r="H32" s="66"/>
+      <c r="I32" s="67"/>
     </row>
     <row r="33" spans="1:9" ht="14.4">
       <c r="A33" s="12"/>
-      <c r="B33" s="15"/>
-      <c r="C33" s="15"/>
-      <c r="D33" s="16"/>
-      <c r="E33" s="32"/>
-      <c r="F33" s="54"/>
+      <c r="B33" s="13"/>
+      <c r="C33" s="13"/>
+      <c r="D33" s="14"/>
+      <c r="F33" s="34"/>
       <c r="G33" s="11"/>
       <c r="H33" s="11"/>
-      <c r="I33" s="17"/>
+      <c r="I33" s="15"/>
     </row>
     <row r="34" spans="1:9" ht="14.4">
       <c r="A34" s="12"/>
-      <c r="B34" s="15"/>
-      <c r="C34" s="55" t="s">
+      <c r="B34" s="13"/>
+      <c r="C34" s="35" t="s">
         <v>105</v>
       </c>
-      <c r="D34" s="16"/>
-      <c r="E34" s="32"/>
-      <c r="F34" s="32"/>
+      <c r="D34" s="14"/>
       <c r="G34" s="11"/>
       <c r="H34" s="11"/>
-      <c r="I34" s="17"/>
+      <c r="I34" s="15"/>
     </row>
     <row r="35" spans="1:9" ht="14.4">
-      <c r="A35" s="18" t="s">
+      <c r="A35" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="B35" s="15"/>
-      <c r="C35" s="56" t="s">
+      <c r="B35" s="13"/>
+      <c r="C35" s="36" t="s">
         <v>107</v>
       </c>
-      <c r="D35" s="15"/>
-      <c r="E35" s="32"/>
-      <c r="F35" s="32"/>
+      <c r="D35" s="13"/>
       <c r="G35" s="11"/>
       <c r="H35" s="11"/>
-      <c r="I35" s="17"/>
+      <c r="I35" s="15"/>
     </row>
     <row r="36" spans="1:9" ht="14.4">
-      <c r="A36" s="19">
+      <c r="A36" s="50">
         <v>46221</v>
       </c>
-      <c r="B36" s="20"/>
-      <c r="C36" s="56" t="s">
+      <c r="B36" s="51"/>
+      <c r="C36" s="36" t="s">
         <v>108</v>
       </c>
-      <c r="D36" s="21"/>
-      <c r="E36" s="32"/>
-      <c r="F36" s="32"/>
-      <c r="G36" s="22" t="s">
+      <c r="D36" s="17"/>
+      <c r="G36" s="52" t="s">
         <v>109</v>
       </c>
-      <c r="H36" s="22"/>
-      <c r="I36" s="23"/>
+      <c r="H36" s="52"/>
+      <c r="I36" s="53"/>
     </row>
     <row r="37" spans="1:9" ht="7.95" customHeight="1">
-      <c r="A37" s="37"/>
-      <c r="B37" s="38"/>
-      <c r="C37" s="38"/>
-      <c r="D37" s="38"/>
-      <c r="E37" s="38"/>
-      <c r="F37" s="38"/>
-      <c r="G37" s="38"/>
-      <c r="H37" s="38"/>
-      <c r="I37" s="39"/>
+      <c r="A37" s="22"/>
+      <c r="B37" s="23"/>
+      <c r="C37" s="23"/>
+      <c r="D37" s="23"/>
+      <c r="E37" s="23"/>
+      <c r="F37" s="23"/>
+      <c r="G37" s="23"/>
+      <c r="H37" s="23"/>
+      <c r="I37" s="24"/>
     </row>
     <row r="43" spans="1:9" ht="19.95" customHeight="1">
-      <c r="A43" s="24" t="s">
+      <c r="A43" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="B43" s="25"/>
-      <c r="C43" s="25"/>
-      <c r="D43" s="25"/>
-      <c r="E43" s="25"/>
-      <c r="F43" s="25"/>
-      <c r="G43" s="25"/>
-      <c r="H43" s="25"/>
-      <c r="I43" s="26"/>
+      <c r="B43" s="55"/>
+      <c r="C43" s="55"/>
+      <c r="D43" s="55"/>
+      <c r="E43" s="55"/>
+      <c r="F43" s="55"/>
+      <c r="G43" s="55"/>
+      <c r="H43" s="55"/>
+      <c r="I43" s="56"/>
     </row>
     <row r="44" spans="1:9" ht="14.4" customHeight="1">
-      <c r="A44" s="28" t="s">
+      <c r="A44" s="57" t="s">
         <v>78</v>
       </c>
-      <c r="B44" s="29"/>
-      <c r="C44" s="29"/>
-      <c r="D44" s="29"/>
-      <c r="E44" s="29"/>
-      <c r="F44" s="29"/>
-      <c r="G44" s="29"/>
-      <c r="H44" s="29"/>
-      <c r="I44" s="30"/>
+      <c r="B44" s="58"/>
+      <c r="C44" s="58"/>
+      <c r="D44" s="58"/>
+      <c r="E44" s="58"/>
+      <c r="F44" s="58"/>
+      <c r="G44" s="58"/>
+      <c r="H44" s="58"/>
+      <c r="I44" s="59"/>
     </row>
     <row r="45" spans="1:9" ht="19.95" customHeight="1">
-      <c r="A45" s="57" t="s">
+      <c r="A45" s="60" t="s">
         <v>111</v>
       </c>
-      <c r="B45" s="58"/>
-      <c r="C45" s="58"/>
-      <c r="D45" s="58"/>
-      <c r="E45" s="58"/>
-      <c r="F45" s="58"/>
-      <c r="G45" s="58"/>
-      <c r="H45" s="58"/>
-      <c r="I45" s="59"/>
+      <c r="B45" s="61"/>
+      <c r="C45" s="61"/>
+      <c r="D45" s="61"/>
+      <c r="E45" s="61"/>
+      <c r="F45" s="61"/>
+      <c r="G45" s="61"/>
+      <c r="H45" s="61"/>
+      <c r="I45" s="62"/>
     </row>
     <row r="46" spans="1:9" ht="19.95" customHeight="1" thickBot="1">
-      <c r="A46" s="40" t="s">
+      <c r="A46" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B46" s="40" t="s">
+      <c r="B46" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="C46" s="41" t="s">
+      <c r="C46" s="26" t="s">
         <v>103</v>
       </c>
-      <c r="D46" s="41" t="s">
+      <c r="D46" s="26" t="s">
         <v>103</v>
       </c>
-      <c r="E46" s="40"/>
-      <c r="F46" s="40" t="s">
+      <c r="E46" s="25"/>
+      <c r="F46" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="G46" s="40" t="s">
+      <c r="G46" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="H46" s="41" t="s">
+      <c r="H46" s="26" t="s">
         <v>103</v>
       </c>
-      <c r="I46" s="41" t="s">
+      <c r="I46" s="26" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="15" customHeight="1">
-      <c r="A47" s="42"/>
-      <c r="B47" s="60" t="s">
+      <c r="A47" s="27"/>
+      <c r="B47" s="37" t="s">
         <v>33</v>
       </c>
-      <c r="C47" s="42"/>
-      <c r="D47" s="42"/>
-      <c r="E47" s="43"/>
-      <c r="F47" s="42"/>
-      <c r="G47" s="60" t="s">
+      <c r="C47" s="27"/>
+      <c r="D47" s="27"/>
+      <c r="E47" s="28"/>
+      <c r="F47" s="27"/>
+      <c r="G47" s="37" t="s">
         <v>52</v>
       </c>
-      <c r="H47" s="42"/>
-      <c r="I47" s="42"/>
+      <c r="H47" s="27"/>
+      <c r="I47" s="27"/>
     </row>
     <row r="48" spans="1:9" ht="15" customHeight="1">
-      <c r="A48" s="42"/>
-      <c r="B48" s="60" t="s">
+      <c r="A48" s="27"/>
+      <c r="B48" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="C48" s="42"/>
-      <c r="D48" s="42"/>
-      <c r="E48" s="43"/>
-      <c r="F48" s="42">
+      <c r="C48" s="27"/>
+      <c r="D48" s="27"/>
+      <c r="E48" s="28"/>
+      <c r="F48" s="27">
         <v>1521</v>
       </c>
-      <c r="G48" s="43" t="s">
+      <c r="G48" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="H48" s="42">
+      <c r="H48" s="27">
         <v>3697</v>
       </c>
-      <c r="I48" s="42"/>
+      <c r="I48" s="27"/>
     </row>
     <row r="49" spans="1:9" ht="15" customHeight="1" thickBot="1">
-      <c r="A49" s="61">
+      <c r="A49" s="38">
         <v>100000</v>
       </c>
-      <c r="B49" s="43" t="s">
+      <c r="B49" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="C49" s="42"/>
-      <c r="D49" s="61">
+      <c r="C49" s="27"/>
+      <c r="D49" s="38">
         <v>100000</v>
       </c>
-      <c r="E49" s="43"/>
-      <c r="F49" s="42">
+      <c r="E49" s="28"/>
+      <c r="F49" s="27">
         <v>42805.9</v>
       </c>
-      <c r="G49" s="43" t="s">
+      <c r="G49" s="28" t="s">
         <v>54</v>
       </c>
-      <c r="H49" s="45">
+      <c r="H49" s="30">
         <v>159270.9</v>
       </c>
-      <c r="I49" s="42">
+      <c r="I49" s="27">
         <f>SUM(H48:H49)</f>
         <v>162967.9</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="15" customHeight="1" thickTop="1">
-      <c r="A50" s="42"/>
-      <c r="B50" s="60" t="s">
+      <c r="A50" s="27"/>
+      <c r="B50" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="C50" s="42"/>
-      <c r="D50" s="42"/>
-      <c r="E50" s="43"/>
-      <c r="F50" s="42"/>
-      <c r="G50" s="60" t="s">
+      <c r="C50" s="27"/>
+      <c r="D50" s="27"/>
+      <c r="E50" s="28"/>
+      <c r="F50" s="27"/>
+      <c r="G50" s="37" t="s">
         <v>55</v>
       </c>
-      <c r="H50" s="42"/>
-      <c r="I50" s="42"/>
+      <c r="H50" s="27"/>
+      <c r="I50" s="27"/>
     </row>
     <row r="51" spans="1:9" ht="15" customHeight="1">
-      <c r="A51" s="42">
+      <c r="A51" s="27">
         <v>3750</v>
       </c>
-      <c r="B51" s="43" t="s">
+      <c r="B51" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="C51" s="42"/>
-      <c r="D51" s="42">
+      <c r="C51" s="27"/>
+      <c r="D51" s="27">
         <v>3750</v>
       </c>
-      <c r="E51" s="43"/>
-      <c r="F51" s="42">
+      <c r="E51" s="28"/>
+      <c r="F51" s="27">
         <v>100</v>
       </c>
-      <c r="G51" s="43" t="s">
+      <c r="G51" s="28" t="s">
         <v>56</v>
       </c>
-      <c r="H51" s="43"/>
-      <c r="I51" s="42">
+      <c r="H51" s="28"/>
+      <c r="I51" s="27">
         <v>100</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="15" customHeight="1">
-      <c r="A52" s="42"/>
-      <c r="B52" s="43" t="s">
+      <c r="A52" s="27"/>
+      <c r="B52" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="C52" s="42"/>
-      <c r="D52" s="42"/>
-      <c r="E52" s="43"/>
-      <c r="F52" s="42"/>
-      <c r="G52" s="60" t="s">
+      <c r="C52" s="27"/>
+      <c r="D52" s="27"/>
+      <c r="E52" s="28"/>
+      <c r="F52" s="27"/>
+      <c r="G52" s="37" t="s">
         <v>57</v>
       </c>
-      <c r="H52" s="42"/>
-      <c r="I52" s="42"/>
+      <c r="H52" s="27"/>
+      <c r="I52" s="27"/>
     </row>
     <row r="53" spans="1:9" ht="15" customHeight="1">
-      <c r="A53" s="42"/>
-      <c r="B53" s="60" t="s">
+      <c r="A53" s="27"/>
+      <c r="B53" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="C53" s="42"/>
-      <c r="D53" s="42"/>
-      <c r="E53" s="43"/>
-      <c r="F53" s="42">
+      <c r="C53" s="27"/>
+      <c r="D53" s="27"/>
+      <c r="E53" s="28"/>
+      <c r="F53" s="27">
         <v>219225</v>
       </c>
-      <c r="G53" s="43" t="s">
+      <c r="G53" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="H53" s="42">
+      <c r="H53" s="27">
         <v>219225</v>
       </c>
-      <c r="I53" s="42"/>
+      <c r="I53" s="27"/>
     </row>
     <row r="54" spans="1:9" ht="15" customHeight="1">
-      <c r="A54" s="42">
+      <c r="A54" s="27">
         <v>257956</v>
       </c>
-      <c r="B54" s="43" t="s">
+      <c r="B54" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="C54" s="42">
+      <c r="C54" s="27">
         <v>257956</v>
       </c>
-      <c r="D54" s="42"/>
-      <c r="E54" s="43"/>
-      <c r="F54" s="42">
+      <c r="D54" s="27"/>
+      <c r="E54" s="28"/>
+      <c r="F54" s="27">
         <v>692085</v>
       </c>
-      <c r="G54" s="43" t="s">
+      <c r="G54" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="H54" s="45">
+      <c r="H54" s="30">
         <v>726065</v>
       </c>
-      <c r="I54" s="42">
+      <c r="I54" s="27">
         <f>SUM(H53:H54)</f>
         <v>945290</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="15" customHeight="1">
-      <c r="A55" s="42"/>
-      <c r="B55" s="43" t="s">
+      <c r="A55" s="27"/>
+      <c r="B55" s="28" t="s">
         <v>89</v>
       </c>
-      <c r="C55" s="45">
+      <c r="C55" s="30">
         <v>51200</v>
       </c>
-      <c r="D55" s="42">
+      <c r="D55" s="27">
         <f>SUM(C54:C55)</f>
         <v>309156</v>
       </c>
-      <c r="E55" s="43"/>
-      <c r="F55" s="42"/>
-      <c r="G55" s="60" t="s">
+      <c r="E55" s="28"/>
+      <c r="F55" s="27"/>
+      <c r="G55" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="H55" s="42"/>
-      <c r="I55" s="42"/>
+      <c r="H55" s="27"/>
+      <c r="I55" s="27"/>
     </row>
     <row r="56" spans="1:9" ht="15" customHeight="1">
-      <c r="A56" s="42"/>
-      <c r="B56" s="60" t="s">
+      <c r="A56" s="27"/>
+      <c r="B56" s="37" t="s">
         <v>41</v>
       </c>
-      <c r="C56" s="42"/>
-      <c r="D56" s="42"/>
-      <c r="E56" s="43"/>
-      <c r="F56" s="42">
+      <c r="C56" s="27"/>
+      <c r="D56" s="27"/>
+      <c r="E56" s="28"/>
+      <c r="F56" s="27">
         <v>21489</v>
       </c>
-      <c r="G56" s="43" t="s">
+      <c r="G56" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="H56" s="42">
+      <c r="H56" s="27">
         <v>36034</v>
       </c>
-      <c r="I56" s="42"/>
+      <c r="I56" s="27"/>
     </row>
     <row r="57" spans="1:9" ht="15" customHeight="1">
-      <c r="A57" s="42">
+      <c r="A57" s="27">
         <v>333039</v>
       </c>
-      <c r="B57" s="43" t="s">
+      <c r="B57" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="C57" s="42">
+      <c r="C57" s="27">
         <v>333039</v>
       </c>
-      <c r="D57" s="42"/>
-      <c r="E57" s="43"/>
-      <c r="F57" s="42">
+      <c r="D57" s="27"/>
+      <c r="E57" s="28"/>
+      <c r="F57" s="27">
         <v>43095</v>
       </c>
-      <c r="G57" s="43" t="s">
+      <c r="G57" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="H57" s="45">
+      <c r="H57" s="30">
         <v>53843</v>
       </c>
-      <c r="I57" s="42">
+      <c r="I57" s="27">
         <f>SUM(H56:H57)</f>
         <v>89877</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="15" customHeight="1">
-      <c r="A58" s="42"/>
-      <c r="B58" s="43" t="s">
+      <c r="A58" s="27"/>
+      <c r="B58" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="C58" s="42">
+      <c r="C58" s="27">
         <v>1464</v>
       </c>
-      <c r="D58" s="42"/>
-      <c r="E58" s="43"/>
-      <c r="F58" s="42"/>
-      <c r="G58" s="60" t="s">
+      <c r="D58" s="27"/>
+      <c r="E58" s="28"/>
+      <c r="F58" s="27"/>
+      <c r="G58" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="H58" s="42"/>
-      <c r="I58" s="42"/>
+      <c r="H58" s="27"/>
+      <c r="I58" s="27"/>
     </row>
     <row r="59" spans="1:9" ht="15" customHeight="1">
-      <c r="A59" s="42"/>
-      <c r="B59" s="43" t="s">
+      <c r="A59" s="27"/>
+      <c r="B59" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="C59" s="45">
+      <c r="C59" s="30">
         <v>16753</v>
       </c>
-      <c r="D59" s="42">
+      <c r="D59" s="27">
         <f>SUM(C57:C59)</f>
         <v>351256</v>
       </c>
-      <c r="E59" s="43"/>
-      <c r="F59" s="42">
+      <c r="E59" s="28"/>
+      <c r="F59" s="27">
         <v>208101</v>
       </c>
-      <c r="G59" s="43" t="s">
+      <c r="G59" s="28" t="s">
         <v>61</v>
       </c>
-      <c r="H59" s="42"/>
-      <c r="I59" s="42">
+      <c r="H59" s="27"/>
+      <c r="I59" s="27">
         <v>345990</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="15" customHeight="1">
-      <c r="A60" s="42"/>
-      <c r="B60" s="60" t="s">
+      <c r="A60" s="27"/>
+      <c r="B60" s="37" t="s">
         <v>44</v>
       </c>
-      <c r="C60" s="42"/>
-      <c r="D60" s="42"/>
-      <c r="E60" s="43"/>
-      <c r="F60" s="43"/>
-      <c r="G60" s="43"/>
-      <c r="H60" s="43"/>
-      <c r="I60" s="43"/>
+      <c r="C60" s="27"/>
+      <c r="D60" s="27"/>
+      <c r="E60" s="28"/>
+      <c r="F60" s="28"/>
+      <c r="G60" s="28"/>
+      <c r="H60" s="28"/>
+      <c r="I60" s="28"/>
     </row>
     <row r="61" spans="1:9" ht="15" customHeight="1">
-      <c r="A61" s="42">
+      <c r="A61" s="27">
         <v>66010</v>
       </c>
-      <c r="B61" s="43" t="s">
+      <c r="B61" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="C61" s="42">
+      <c r="C61" s="27">
         <v>66010</v>
       </c>
-      <c r="D61" s="42"/>
-      <c r="E61" s="43"/>
-      <c r="F61" s="42"/>
-      <c r="G61" s="60" t="s">
+      <c r="D61" s="27"/>
+      <c r="E61" s="28"/>
+      <c r="F61" s="27"/>
+      <c r="G61" s="37" t="s">
         <v>87</v>
       </c>
-      <c r="H61" s="42"/>
-      <c r="I61" s="42"/>
+      <c r="H61" s="27"/>
+      <c r="I61" s="27"/>
     </row>
     <row r="62" spans="1:9" ht="15" customHeight="1">
-      <c r="A62" s="42"/>
-      <c r="B62" s="43" t="s">
+      <c r="A62" s="27"/>
+      <c r="B62" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="C62" s="45">
+      <c r="C62" s="30">
         <v>5400</v>
       </c>
-      <c r="D62" s="42">
+      <c r="D62" s="27">
         <f>SUM(C61:C62)</f>
         <v>71410</v>
       </c>
-      <c r="E62" s="43"/>
-      <c r="F62" s="42">
+      <c r="E62" s="28"/>
+      <c r="F62" s="27">
         <v>1970</v>
       </c>
-      <c r="G62" s="43" t="s">
+      <c r="G62" s="28" t="s">
         <v>88</v>
       </c>
-      <c r="H62" s="42"/>
-      <c r="I62" s="42">
+      <c r="H62" s="27"/>
+      <c r="I62" s="27">
         <v>1970</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="15" customHeight="1">
-      <c r="A63" s="42"/>
-      <c r="B63" s="60" t="s">
+      <c r="A63" s="27"/>
+      <c r="B63" s="37" t="s">
         <v>64</v>
       </c>
-      <c r="C63" s="42"/>
-      <c r="D63" s="42"/>
-      <c r="E63" s="43"/>
-      <c r="F63" s="42">
+      <c r="C63" s="27"/>
+      <c r="D63" s="27"/>
+      <c r="E63" s="28"/>
+      <c r="F63" s="27">
         <v>4230</v>
       </c>
-      <c r="G63" s="43" t="s">
+      <c r="G63" s="28" t="s">
         <v>90</v>
       </c>
-      <c r="H63" s="43"/>
-      <c r="I63" s="42">
+      <c r="H63" s="28"/>
+      <c r="I63" s="27">
         <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="15" customHeight="1">
-      <c r="A64" s="42">
+      <c r="A64" s="27">
         <v>35882</v>
       </c>
-      <c r="B64" s="43" t="s">
+      <c r="B64" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="C64" s="42"/>
-      <c r="D64" s="42">
+      <c r="C64" s="27"/>
+      <c r="D64" s="27">
         <v>35882</v>
       </c>
-      <c r="E64" s="43"/>
-      <c r="F64" s="42">
+      <c r="E64" s="28"/>
+      <c r="F64" s="27">
         <v>4804</v>
       </c>
-      <c r="G64" s="43" t="s">
+      <c r="G64" s="28" t="s">
         <v>92</v>
       </c>
-      <c r="H64" s="43"/>
-      <c r="I64" s="42">
+      <c r="H64" s="28"/>
+      <c r="I64" s="27">
         <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:11" ht="15" customHeight="1">
-      <c r="A65" s="43"/>
-      <c r="B65" s="60" t="s">
+      <c r="A65" s="28"/>
+      <c r="B65" s="37" t="s">
         <v>45</v>
       </c>
-      <c r="C65" s="43"/>
-      <c r="D65" s="43"/>
-      <c r="E65" s="43"/>
-      <c r="F65" s="42">
+      <c r="C65" s="28"/>
+      <c r="D65" s="28"/>
+      <c r="E65" s="28"/>
+      <c r="F65" s="27">
         <v>6958</v>
       </c>
-      <c r="G65" s="43" t="s">
+      <c r="G65" s="28" t="s">
         <v>95</v>
       </c>
-      <c r="H65" s="42"/>
-      <c r="I65" s="42">
+      <c r="H65" s="27"/>
+      <c r="I65" s="27">
         <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:11" ht="15" customHeight="1">
-      <c r="A66" s="42">
+      <c r="A66" s="27">
         <v>50</v>
       </c>
-      <c r="B66" s="43" t="s">
+      <c r="B66" s="28" t="s">
         <v>50</v>
       </c>
-      <c r="C66" s="42"/>
-      <c r="D66" s="42">
+      <c r="C66" s="27"/>
+      <c r="D66" s="27">
         <v>3401</v>
       </c>
-      <c r="E66" s="43"/>
-      <c r="F66" s="42">
+      <c r="E66" s="28"/>
+      <c r="F66" s="27">
         <v>0</v>
       </c>
-      <c r="G66" s="43" t="s">
+      <c r="G66" s="28" t="s">
         <v>100</v>
       </c>
-      <c r="H66" s="42"/>
-      <c r="I66" s="42">
+      <c r="H66" s="27"/>
+      <c r="I66" s="27">
         <v>6586</v>
       </c>
     </row>
     <row r="67" spans="1:11" ht="15" customHeight="1">
-      <c r="A67" s="42">
+      <c r="A67" s="27">
         <v>250000</v>
       </c>
-      <c r="B67" s="43" t="s">
+      <c r="B67" s="28" t="s">
         <v>65</v>
       </c>
-      <c r="C67" s="42"/>
-      <c r="D67" s="42">
+      <c r="C67" s="27"/>
+      <c r="D67" s="27">
         <v>250000</v>
       </c>
-      <c r="E67" s="43"/>
-      <c r="F67" s="42"/>
-      <c r="G67" s="60"/>
-      <c r="H67" s="42"/>
-      <c r="I67" s="42"/>
+      <c r="E67" s="28"/>
+      <c r="F67" s="27"/>
+      <c r="G67" s="37"/>
+      <c r="H67" s="27"/>
+      <c r="I67" s="27"/>
     </row>
     <row r="68" spans="1:11" ht="15" customHeight="1">
-      <c r="A68" s="42"/>
-      <c r="B68" s="43" t="s">
+      <c r="A68" s="27"/>
+      <c r="B68" s="28" t="s">
         <v>101</v>
       </c>
-      <c r="C68" s="42"/>
-      <c r="D68" s="42">
+      <c r="C68" s="27"/>
+      <c r="D68" s="27">
         <v>150000</v>
       </c>
-      <c r="E68" s="43"/>
-      <c r="F68" s="42"/>
-      <c r="G68" s="43"/>
-      <c r="H68" s="42"/>
-      <c r="I68" s="42"/>
-      <c r="K68" s="62"/>
+      <c r="E68" s="28"/>
+      <c r="F68" s="27"/>
+      <c r="G68" s="28"/>
+      <c r="H68" s="27"/>
+      <c r="I68" s="27"/>
+      <c r="K68" s="39"/>
     </row>
     <row r="69" spans="1:11" ht="15" customHeight="1">
-      <c r="A69" s="42"/>
-      <c r="B69" s="60" t="s">
+      <c r="A69" s="27"/>
+      <c r="B69" s="37" t="s">
         <v>46</v>
       </c>
-      <c r="C69" s="42"/>
-      <c r="D69" s="42"/>
-      <c r="E69" s="43"/>
-      <c r="F69" s="42"/>
-      <c r="G69" s="60" t="s">
+      <c r="C69" s="27"/>
+      <c r="D69" s="27"/>
+      <c r="E69" s="28"/>
+      <c r="F69" s="27"/>
+      <c r="G69" s="37" t="s">
         <v>62</v>
       </c>
-      <c r="H69" s="42"/>
-      <c r="I69" s="42"/>
+      <c r="H69" s="27"/>
+      <c r="I69" s="27"/>
     </row>
     <row r="70" spans="1:11" ht="15" customHeight="1">
-      <c r="A70" s="42">
+      <c r="A70" s="27">
         <v>1500</v>
       </c>
-      <c r="B70" s="43" t="s">
+      <c r="B70" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="C70" s="42">
+      <c r="C70" s="27">
         <v>1800</v>
       </c>
-      <c r="D70" s="42"/>
-      <c r="E70" s="43"/>
-      <c r="F70" s="42">
+      <c r="D70" s="27"/>
+      <c r="E70" s="28"/>
+      <c r="F70" s="27">
         <v>16623</v>
       </c>
-      <c r="G70" s="43" t="s">
+      <c r="G70" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="H70" s="42">
+      <c r="H70" s="27">
         <v>16623</v>
       </c>
-      <c r="I70" s="42"/>
+      <c r="I70" s="27"/>
     </row>
     <row r="71" spans="1:11" ht="15" customHeight="1">
-      <c r="A71" s="42">
+      <c r="A71" s="27">
         <v>1500</v>
       </c>
-      <c r="B71" s="43" t="s">
+      <c r="B71" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="C71" s="42">
+      <c r="C71" s="27">
         <v>3000</v>
       </c>
-      <c r="D71" s="42"/>
-      <c r="E71" s="43"/>
-      <c r="F71" s="43"/>
-      <c r="G71" s="43" t="s">
+      <c r="D71" s="27"/>
+      <c r="E71" s="28"/>
+      <c r="F71" s="28"/>
+      <c r="G71" s="28" t="s">
         <v>81</v>
       </c>
-      <c r="H71" s="42">
+      <c r="H71" s="27">
         <v>0</v>
       </c>
-      <c r="I71" s="43"/>
+      <c r="I71" s="28"/>
     </row>
     <row r="72" spans="1:11" ht="15" customHeight="1">
-      <c r="A72" s="42">
+      <c r="A72" s="27">
         <v>3500</v>
       </c>
-      <c r="B72" s="43" t="s">
+      <c r="B72" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="C72" s="42">
+      <c r="C72" s="27">
         <v>3500</v>
       </c>
-      <c r="D72" s="42"/>
-      <c r="E72" s="43"/>
-      <c r="F72" s="42"/>
-      <c r="G72" s="43" t="s">
+      <c r="D72" s="27"/>
+      <c r="E72" s="28"/>
+      <c r="F72" s="27"/>
+      <c r="G72" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="H72" s="45">
+      <c r="H72" s="30">
         <v>-2493</v>
       </c>
-      <c r="I72" s="42">
+      <c r="I72" s="27">
         <f>SUM(H70:H72)</f>
         <v>14130</v>
       </c>
     </row>
     <row r="73" spans="1:11" ht="15" customHeight="1">
-      <c r="A73" s="42">
+      <c r="A73" s="27">
         <v>10532</v>
       </c>
-      <c r="B73" s="43" t="s">
+      <c r="B73" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="C73" s="42">
+      <c r="C73" s="27">
         <v>11000</v>
       </c>
-      <c r="D73" s="42"/>
-      <c r="E73" s="43"/>
-      <c r="F73" s="42"/>
-      <c r="G73" s="43"/>
-      <c r="H73" s="42"/>
-      <c r="I73" s="42"/>
+      <c r="D73" s="27"/>
+      <c r="E73" s="28"/>
+      <c r="F73" s="27"/>
+      <c r="G73" s="28"/>
+      <c r="H73" s="27"/>
+      <c r="I73" s="27"/>
     </row>
     <row r="74" spans="1:11" ht="15" customHeight="1">
-      <c r="A74" s="42">
+      <c r="A74" s="27">
         <v>1880</v>
       </c>
-      <c r="B74" s="43" t="s">
+      <c r="B74" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="C74" s="42">
+      <c r="C74" s="27">
         <v>1910</v>
       </c>
-      <c r="D74" s="42"/>
-      <c r="E74" s="43"/>
-      <c r="F74" s="42">
+      <c r="D74" s="27"/>
+      <c r="E74" s="28"/>
+      <c r="F74" s="27">
         <v>12425</v>
       </c>
-      <c r="G74" s="60" t="s">
+      <c r="G74" s="37" t="s">
         <v>82</v>
       </c>
-      <c r="H74" s="43"/>
-      <c r="I74" s="43"/>
+      <c r="H74" s="28"/>
+      <c r="I74" s="28"/>
     </row>
     <row r="75" spans="1:11" ht="15" customHeight="1">
-      <c r="A75" s="42">
+      <c r="A75" s="27">
         <v>4630</v>
       </c>
-      <c r="B75" s="31" t="s">
+      <c r="B75" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="C75" s="45">
+      <c r="C75" s="30">
         <v>5456</v>
       </c>
-      <c r="D75" s="63">
+      <c r="D75" s="40">
         <f>SUM(C70:C75)</f>
         <v>26666</v>
       </c>
-      <c r="E75" s="43"/>
-      <c r="F75" s="43"/>
-      <c r="G75" s="43" t="s">
+      <c r="E75" s="28"/>
+      <c r="F75" s="28"/>
+      <c r="G75" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="H75" s="42">
+      <c r="H75" s="27">
         <v>12425</v>
       </c>
-      <c r="I75" s="43"/>
-      <c r="K75" s="62"/>
+      <c r="I75" s="28"/>
+      <c r="K75" s="39"/>
     </row>
     <row r="76" spans="1:11" ht="15" customHeight="1">
-      <c r="A76" s="43"/>
-      <c r="B76" s="43"/>
-      <c r="C76" s="43"/>
-      <c r="D76" s="63"/>
-      <c r="E76" s="43"/>
-      <c r="F76" s="42"/>
-      <c r="G76" s="43" t="s">
+      <c r="A76" s="28"/>
+      <c r="B76" s="28"/>
+      <c r="C76" s="28"/>
+      <c r="D76" s="40"/>
+      <c r="E76" s="28"/>
+      <c r="F76" s="27"/>
+      <c r="G76" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="H76" s="45">
+      <c r="H76" s="30">
         <v>-1864</v>
       </c>
-      <c r="I76" s="43"/>
+      <c r="I76" s="28"/>
     </row>
     <row r="77" spans="1:11" ht="15" customHeight="1">
-      <c r="A77" s="42">
+      <c r="A77" s="27">
         <v>305202.90000000002</v>
       </c>
-      <c r="B77" s="60" t="s">
+      <c r="B77" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="C77" s="42"/>
-      <c r="D77" s="42"/>
-      <c r="E77" s="43"/>
-      <c r="F77" s="43"/>
-      <c r="G77" s="43"/>
-      <c r="H77" s="42"/>
-      <c r="I77" s="42">
+      <c r="C77" s="27"/>
+      <c r="D77" s="27"/>
+      <c r="E77" s="28"/>
+      <c r="F77" s="28"/>
+      <c r="G77" s="28"/>
+      <c r="H77" s="27"/>
+      <c r="I77" s="27">
         <f>SUM(H75:H76)</f>
         <v>10561</v>
       </c>
     </row>
     <row r="78" spans="1:11" ht="15" customHeight="1">
-      <c r="A78" s="42"/>
-      <c r="B78" s="43" t="s">
+      <c r="A78" s="27"/>
+      <c r="B78" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="C78" s="42">
+      <c r="C78" s="27">
         <v>305202.90000000002</v>
       </c>
-      <c r="D78" s="63"/>
-      <c r="E78" s="43"/>
-      <c r="F78" s="42"/>
-      <c r="G78" s="43"/>
-      <c r="H78" s="42"/>
-      <c r="I78" s="42"/>
+      <c r="D78" s="40"/>
+      <c r="E78" s="28"/>
+      <c r="F78" s="27"/>
+      <c r="G78" s="28"/>
+      <c r="H78" s="27"/>
+      <c r="I78" s="27"/>
     </row>
     <row r="79" spans="1:11" ht="15" customHeight="1">
-      <c r="A79" s="42"/>
-      <c r="B79" s="43" t="s">
+      <c r="A79" s="27"/>
+      <c r="B79" s="28" t="s">
         <v>84</v>
       </c>
-      <c r="C79" s="42">
+      <c r="C79" s="27">
         <f>D26</f>
         <v>70748</v>
       </c>
-      <c r="D79" s="42">
+      <c r="D79" s="27">
         <f>SUM(C78:C79)</f>
         <v>375950.9</v>
       </c>
-      <c r="E79" s="43"/>
-      <c r="F79" s="42"/>
-      <c r="G79" s="43"/>
-      <c r="H79" s="42"/>
-      <c r="I79" s="42"/>
-    </row>
-    <row r="80" spans="1:11" s="48" customFormat="1" ht="19.95" customHeight="1" thickBot="1">
-      <c r="A80" s="46">
+      <c r="E79" s="28"/>
+      <c r="F79" s="27"/>
+      <c r="G79" s="28"/>
+      <c r="H79" s="27"/>
+      <c r="I79" s="27"/>
+    </row>
+    <row r="80" spans="1:11" s="33" customFormat="1" ht="19.95" customHeight="1" thickBot="1">
+      <c r="A80" s="31">
         <f>SUM(A51:A79)</f>
         <v>1275431.8999999999</v>
       </c>
-      <c r="B80" s="64" t="s">
+      <c r="B80" s="41" t="s">
         <v>112</v>
       </c>
-      <c r="C80" s="46"/>
-      <c r="D80" s="46">
+      <c r="C80" s="31"/>
+      <c r="D80" s="31">
         <f>SUM(D51:D79)</f>
         <v>1577471.9</v>
       </c>
-      <c r="E80" s="47"/>
-      <c r="F80" s="46">
+      <c r="E80" s="32"/>
+      <c r="F80" s="31">
         <f>SUM(F47:F79)</f>
         <v>1275431.8999999999</v>
       </c>
-      <c r="G80" s="64" t="s">
+      <c r="G80" s="41" t="s">
         <v>112</v>
       </c>
-      <c r="H80" s="46"/>
-      <c r="I80" s="46">
+      <c r="H80" s="31"/>
+      <c r="I80" s="31">
         <f>SUM(I47:I79)</f>
         <v>1577471.9</v>
       </c>
     </row>
     <row r="81" spans="1:9" ht="8.1" customHeight="1" thickTop="1">
-      <c r="A81" s="31"/>
-      <c r="B81" s="32"/>
-      <c r="C81" s="32"/>
-      <c r="D81" s="32"/>
-      <c r="E81" s="32"/>
-      <c r="F81" s="32"/>
-      <c r="G81" s="32"/>
-      <c r="H81" s="32"/>
-      <c r="I81" s="33"/>
+      <c r="A81" s="20"/>
+      <c r="I81" s="21"/>
     </row>
     <row r="82" spans="1:9" ht="14.4">
       <c r="A82" s="10" t="s">
@@ -2719,129 +2680,123 @@
       <c r="B82" s="11"/>
       <c r="C82" s="11"/>
       <c r="D82" s="11"/>
-      <c r="E82" s="32"/>
-      <c r="F82" s="32"/>
-      <c r="G82" s="49"/>
-      <c r="H82" s="32"/>
-      <c r="I82" s="33"/>
+      <c r="G82" s="19"/>
+      <c r="I82" s="21"/>
     </row>
     <row r="83" spans="1:9" ht="15.75" customHeight="1">
       <c r="A83" s="12"/>
-      <c r="B83" s="13"/>
-      <c r="C83" s="13"/>
-      <c r="D83" s="13"/>
-      <c r="E83" s="32"/>
-      <c r="F83" s="32"/>
-      <c r="G83" s="50" t="s">
+      <c r="B83" s="63"/>
+      <c r="C83" s="63"/>
+      <c r="D83" s="63"/>
+      <c r="G83" s="64" t="s">
         <v>110</v>
       </c>
-      <c r="H83" s="50"/>
-      <c r="I83" s="51"/>
+      <c r="H83" s="64"/>
+      <c r="I83" s="65"/>
     </row>
     <row r="84" spans="1:9" ht="14.4">
       <c r="A84" s="12"/>
-      <c r="B84" s="14"/>
-      <c r="C84" s="14"/>
-      <c r="D84" s="14"/>
-      <c r="E84" s="32"/>
-      <c r="F84" s="32"/>
-      <c r="G84" s="52"/>
-      <c r="H84" s="52"/>
-      <c r="I84" s="53"/>
+      <c r="B84" s="68"/>
+      <c r="C84" s="68"/>
+      <c r="D84" s="68"/>
+      <c r="G84" s="66"/>
+      <c r="H84" s="66"/>
+      <c r="I84" s="67"/>
     </row>
     <row r="85" spans="1:9" ht="14.4">
       <c r="A85" s="12"/>
-      <c r="B85" s="15"/>
-      <c r="C85" s="15"/>
-      <c r="D85" s="16"/>
-      <c r="E85" s="32"/>
-      <c r="F85" s="54"/>
+      <c r="B85" s="13"/>
+      <c r="C85" s="13"/>
+      <c r="D85" s="14"/>
+      <c r="F85" s="34"/>
       <c r="G85" s="11"/>
       <c r="H85" s="11"/>
-      <c r="I85" s="17"/>
+      <c r="I85" s="15"/>
     </row>
     <row r="86" spans="1:9" ht="14.4">
       <c r="A86" s="12"/>
-      <c r="B86" s="15"/>
-      <c r="C86" s="55" t="s">
+      <c r="B86" s="13"/>
+      <c r="C86" s="35" t="s">
         <v>105</v>
       </c>
-      <c r="D86" s="16"/>
-      <c r="E86" s="32"/>
-      <c r="F86" s="32"/>
+      <c r="D86" s="14"/>
       <c r="G86" s="11"/>
       <c r="H86" s="11"/>
-      <c r="I86" s="17"/>
+      <c r="I86" s="15"/>
     </row>
     <row r="87" spans="1:9" ht="14.4">
-      <c r="A87" s="18" t="s">
+      <c r="A87" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="B87" s="15"/>
-      <c r="C87" s="56" t="s">
+      <c r="B87" s="13"/>
+      <c r="C87" s="36" t="s">
         <v>107</v>
       </c>
-      <c r="D87" s="15"/>
-      <c r="E87" s="32"/>
-      <c r="F87" s="32"/>
+      <c r="D87" s="13"/>
       <c r="G87" s="11"/>
       <c r="H87" s="11"/>
-      <c r="I87" s="17"/>
+      <c r="I87" s="15"/>
     </row>
     <row r="88" spans="1:9" ht="14.4">
-      <c r="A88" s="19">
+      <c r="A88" s="50">
         <v>46221</v>
       </c>
-      <c r="B88" s="20"/>
-      <c r="C88" s="56" t="s">
+      <c r="B88" s="51"/>
+      <c r="C88" s="36" t="s">
         <v>108</v>
       </c>
-      <c r="D88" s="21"/>
-      <c r="E88" s="32"/>
-      <c r="F88" s="32"/>
-      <c r="G88" s="22" t="s">
+      <c r="D88" s="17"/>
+      <c r="G88" s="52" t="s">
         <v>109</v>
       </c>
-      <c r="H88" s="22"/>
-      <c r="I88" s="23"/>
+      <c r="H88" s="52"/>
+      <c r="I88" s="53"/>
     </row>
     <row r="89" spans="1:9" ht="7.95" customHeight="1">
-      <c r="A89" s="37"/>
-      <c r="B89" s="38"/>
-      <c r="C89" s="38"/>
-      <c r="D89" s="38"/>
-      <c r="E89" s="38"/>
-      <c r="F89" s="38"/>
-      <c r="G89" s="38"/>
-      <c r="H89" s="38"/>
-      <c r="I89" s="39"/>
+      <c r="A89" s="22"/>
+      <c r="B89" s="23"/>
+      <c r="C89" s="23"/>
+      <c r="D89" s="23"/>
+      <c r="E89" s="23"/>
+      <c r="F89" s="23"/>
+      <c r="G89" s="23"/>
+      <c r="H89" s="23"/>
+      <c r="I89" s="24"/>
     </row>
     <row r="90" spans="1:9">
-      <c r="A90" s="63"/>
-      <c r="C90" s="63"/>
-      <c r="D90" s="63"/>
-      <c r="F90" s="63"/>
-      <c r="H90" s="63"/>
-      <c r="I90" s="63"/>
+      <c r="A90" s="40"/>
+      <c r="C90" s="40"/>
+      <c r="D90" s="40"/>
+      <c r="F90" s="40"/>
+      <c r="H90" s="40"/>
+      <c r="I90" s="40"/>
     </row>
     <row r="91" spans="1:9">
-      <c r="A91" s="63"/>
-      <c r="C91" s="63"/>
-      <c r="D91" s="63"/>
-      <c r="F91" s="63"/>
-      <c r="H91" s="63"/>
-      <c r="I91" s="63"/>
+      <c r="A91" s="40"/>
+      <c r="C91" s="40"/>
+      <c r="D91" s="40"/>
+      <c r="F91" s="40"/>
+      <c r="H91" s="40"/>
+      <c r="I91" s="40"/>
     </row>
     <row r="92" spans="1:9">
-      <c r="A92" s="63"/>
-      <c r="C92" s="63"/>
-      <c r="D92" s="63"/>
-      <c r="F92" s="63"/>
-      <c r="H92" s="63"/>
-      <c r="I92" s="63"/>
+      <c r="A92" s="40"/>
+      <c r="C92" s="40"/>
+      <c r="D92" s="40"/>
+      <c r="F92" s="40"/>
+      <c r="H92" s="40"/>
+      <c r="I92" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="G31:I32"/>
+    <mergeCell ref="G36:I36"/>
     <mergeCell ref="A88:B88"/>
     <mergeCell ref="G88:I88"/>
     <mergeCell ref="A43:I43"/>
@@ -2850,14 +2805,6 @@
     <mergeCell ref="B83:D83"/>
     <mergeCell ref="G83:I84"/>
     <mergeCell ref="B84:D84"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="G31:I32"/>
-    <mergeCell ref="G36:I36"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A4:I4"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.19685039370078741" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -2885,29 +2832,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="18">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="73" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
-      <c r="I1" s="67"/>
+      <c r="B1" s="73"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73"/>
+      <c r="G1" s="73"/>
+      <c r="H1" s="73"/>
+      <c r="I1" s="42"/>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="66" t="s">
+      <c r="A2" s="72" t="s">
         <v>96</v>
       </c>
-      <c r="B2" s="66"/>
-      <c r="C2" s="66"/>
-      <c r="D2" s="66"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="66"/>
-      <c r="G2" s="66"/>
-      <c r="H2" s="66"/>
+      <c r="B2" s="72"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="72"/>
+      <c r="G2" s="72"/>
+      <c r="H2" s="72"/>
     </row>
     <row r="4" spans="1:12" s="3" customFormat="1" ht="13.8">
       <c r="A4" s="6" t="s">
@@ -3094,7 +3041,7 @@
       <c r="B12" s="1">
         <v>45239</v>
       </c>
-      <c r="C12" s="70">
+      <c r="C12" s="8">
         <v>35038</v>
       </c>
       <c r="D12" s="1">
@@ -3103,14 +3050,14 @@
       <c r="E12" s="8">
         <v>43098</v>
       </c>
-      <c r="F12" s="70">
+      <c r="F12" s="8">
         <f>945+2798-279+1003-302</f>
         <v>4165</v>
       </c>
-      <c r="G12" s="70">
+      <c r="G12" s="8">
         <v>1003</v>
       </c>
-      <c r="H12" s="70">
+      <c r="H12" s="8">
         <v>302</v>
       </c>
       <c r="I12" s="8"/>
@@ -3119,13 +3066,13 @@
       <c r="L12" s="8"/>
     </row>
     <row r="13" spans="1:12" ht="15" thickBot="1">
-      <c r="A13" s="69"/>
-      <c r="B13" s="71"/>
+      <c r="A13" s="44"/>
+      <c r="B13" s="45"/>
       <c r="C13" s="9">
         <f>SUM(C8:C12)</f>
         <v>219225</v>
       </c>
-      <c r="D13" s="71"/>
+      <c r="D13" s="45"/>
       <c r="E13" s="9"/>
       <c r="F13" s="9">
         <f>SUM(F8:F12)</f>
@@ -3309,20 +3256,20 @@
       <c r="B22" s="1">
         <v>45874</v>
       </c>
-      <c r="C22" s="70">
+      <c r="C22" s="8">
         <v>462252</v>
       </c>
       <c r="D22" s="1">
         <v>46239</v>
       </c>
-      <c r="F22" s="70">
+      <c r="F22" s="8">
         <f>20565-2056</f>
         <v>18509</v>
       </c>
-      <c r="G22" s="70">
+      <c r="G22" s="8">
         <v>20565</v>
       </c>
-      <c r="H22" s="70">
+      <c r="H22" s="8">
         <v>2056</v>
       </c>
       <c r="I22" s="8"/>
@@ -3331,13 +3278,13 @@
       <c r="L22" s="8"/>
     </row>
     <row r="23" spans="1:12" ht="15" thickBot="1">
-      <c r="A23" s="69"/>
-      <c r="B23" s="71"/>
+      <c r="A23" s="44"/>
+      <c r="B23" s="45"/>
       <c r="C23" s="9">
         <f>SUM(C18:C22)</f>
         <v>726065</v>
       </c>
-      <c r="D23" s="71"/>
+      <c r="D23" s="45"/>
       <c r="E23" s="9"/>
       <c r="F23" s="9">
         <f>SUM(F18:F22)</f>
@@ -3372,31 +3319,31 @@
       <c r="K25" s="8"/>
       <c r="L25" s="8"/>
     </row>
-    <row r="26" spans="1:12" s="74" customFormat="1" ht="15" thickBot="1">
-      <c r="A26" s="68" t="s">
+    <row r="26" spans="1:12" s="48" customFormat="1" ht="15" thickBot="1">
+      <c r="A26" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="B26" s="72"/>
-      <c r="C26" s="73">
+      <c r="B26" s="46"/>
+      <c r="C26" s="47">
         <f>C13+C23</f>
         <v>945290</v>
       </c>
-      <c r="D26" s="72"/>
-      <c r="E26" s="73"/>
-      <c r="F26" s="73">
+      <c r="D26" s="46"/>
+      <c r="E26" s="47"/>
+      <c r="F26" s="47">
         <f>F13+F23</f>
         <v>89877</v>
       </c>
-      <c r="G26" s="73">
+      <c r="G26" s="47">
         <f>G13+G23</f>
         <v>65859</v>
       </c>
-      <c r="H26" s="73">
+      <c r="H26" s="47">
         <f>H13+H23</f>
         <v>6586</v>
       </c>
-      <c r="J26" s="75"/>
-      <c r="K26" s="75"/>
+      <c r="J26" s="49"/>
+      <c r="K26" s="49"/>
     </row>
     <row r="27" spans="1:12" ht="15" thickTop="1"/>
     <row r="31" spans="1:12">

--- a/Bharat/Dahisaralkachs/Final Acoounts 31.03.2026.xlsx
+++ b/Bharat/Dahisaralkachs/Final Acoounts 31.03.2026.xlsx
@@ -1,23 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BHARAT\2025-2026\BCB\Bharat\Dahisaralkachs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDA98775-8BB8-4AB3-ABF3-8461AB22752E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E95BF351-53CA-44F4-BBBD-3C240D632B09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Final Accounts" sheetId="1" r:id="rId1"/>
     <sheet name="FD Register" sheetId="5" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="6" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'FD Register'!$A$1:$H$27</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'FD Register'!$A$1:$I$27</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Final Accounts'!$A$1:$I$86</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -346,9 +348,6 @@
   </si>
   <si>
     <t>Renewed</t>
-  </si>
-  <si>
-    <t>To Amount W/off</t>
   </si>
   <si>
     <t>TDS 2025-26</t>
@@ -438,6 +437,9 @@
   </si>
   <si>
     <t>TOTAL :-</t>
+  </si>
+  <si>
+    <t>Less : TDS Receivables Written Off</t>
   </si>
 </sst>
 </file>
@@ -910,6 +912,18 @@
     <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -945,18 +959,6 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1286,7 +1288,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K92"/>
+  <dimension ref="A1:K89"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="13.5546875" style="18" customWidth="1"/>
@@ -1302,30 +1304,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="19.95" customHeight="1">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="58" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="56"/>
+      <c r="B1" s="59"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="59"/>
+      <c r="G1" s="59"/>
+      <c r="H1" s="59"/>
+      <c r="I1" s="60"/>
     </row>
     <row r="2" spans="1:9" ht="14.4" customHeight="1">
-      <c r="A2" s="57" t="s">
+      <c r="A2" s="61" t="s">
         <v>78</v>
       </c>
-      <c r="B2" s="58"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="59"/>
+      <c r="B2" s="62"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="63"/>
     </row>
     <row r="3" spans="1:9" ht="7.95" customHeight="1">
       <c r="A3" s="20"/>
@@ -1333,7 +1335,7 @@
     </row>
     <row r="4" spans="1:9" ht="16.8" customHeight="1">
       <c r="A4" s="69" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
@@ -1363,10 +1365,10 @@
         <v>2</v>
       </c>
       <c r="C6" s="26" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D6" s="26" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E6" s="25"/>
       <c r="F6" s="25" t="s">
@@ -1376,10 +1378,10 @@
         <v>3</v>
       </c>
       <c r="H6" s="26" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I6" s="26" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="10.050000000000001" customHeight="1">
@@ -1414,14 +1416,14 @@
     </row>
     <row r="9" spans="1:9" ht="15" customHeight="1">
       <c r="A9" s="27">
-        <v>0</v>
+        <v>48778</v>
       </c>
       <c r="B9" s="28" t="s">
-        <v>99</v>
+        <v>17</v>
       </c>
       <c r="C9" s="27"/>
       <c r="D9" s="27">
-        <v>15992</v>
+        <v>44540</v>
       </c>
       <c r="E9" s="28"/>
       <c r="F9" s="27">
@@ -1437,14 +1439,14 @@
     </row>
     <row r="10" spans="1:9" ht="15" customHeight="1">
       <c r="A10" s="27">
-        <v>48778</v>
+        <v>21430</v>
       </c>
       <c r="B10" s="28" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C10" s="27"/>
       <c r="D10" s="27">
-        <v>44540</v>
+        <v>22850</v>
       </c>
       <c r="E10" s="28"/>
       <c r="F10" s="27">
@@ -1460,14 +1462,14 @@
     </row>
     <row r="11" spans="1:9" ht="15" customHeight="1">
       <c r="A11" s="27">
-        <v>21430</v>
+        <v>1500</v>
       </c>
       <c r="B11" s="28" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C11" s="27"/>
       <c r="D11" s="27">
-        <v>22850</v>
+        <v>1500</v>
       </c>
       <c r="E11" s="28"/>
       <c r="F11" s="27">
@@ -1483,14 +1485,14 @@
     </row>
     <row r="12" spans="1:9" ht="15" customHeight="1">
       <c r="A12" s="27">
-        <v>1500</v>
+        <v>3500</v>
       </c>
       <c r="B12" s="28" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C12" s="27"/>
       <c r="D12" s="27">
-        <v>1500</v>
+        <v>3500</v>
       </c>
       <c r="E12" s="28"/>
       <c r="F12" s="27">
@@ -1506,14 +1508,14 @@
     </row>
     <row r="13" spans="1:9" ht="15" customHeight="1">
       <c r="A13" s="27">
-        <v>3500</v>
+        <v>2705</v>
       </c>
       <c r="B13" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C13" s="27"/>
       <c r="D13" s="27">
-        <v>3500</v>
+        <v>848</v>
       </c>
       <c r="E13" s="28"/>
       <c r="F13" s="27">
@@ -1529,14 +1531,14 @@
     </row>
     <row r="14" spans="1:9" ht="15" customHeight="1">
       <c r="A14" s="27">
-        <v>2705</v>
+        <v>26098</v>
       </c>
       <c r="B14" s="28" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C14" s="27"/>
       <c r="D14" s="27">
-        <v>848</v>
+        <v>42148</v>
       </c>
       <c r="E14" s="28"/>
       <c r="F14" s="27">
@@ -1552,14 +1554,14 @@
     </row>
     <row r="15" spans="1:9" ht="15" customHeight="1">
       <c r="A15" s="27">
-        <v>26098</v>
+        <v>0</v>
       </c>
       <c r="B15" s="28" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C15" s="27"/>
       <c r="D15" s="27">
-        <v>42148</v>
+        <v>177</v>
       </c>
       <c r="E15" s="28"/>
       <c r="F15" s="29">
@@ -1575,14 +1577,14 @@
     </row>
     <row r="16" spans="1:9" ht="15" customHeight="1">
       <c r="A16" s="27">
-        <v>0</v>
+        <v>5187</v>
       </c>
       <c r="B16" s="28" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C16" s="27"/>
       <c r="D16" s="27">
-        <v>177</v>
+        <v>4357</v>
       </c>
       <c r="E16" s="28"/>
       <c r="F16" s="27">
@@ -1598,14 +1600,14 @@
     </row>
     <row r="17" spans="1:9" ht="15" customHeight="1">
       <c r="A17" s="27">
-        <v>5187</v>
+        <v>2105</v>
       </c>
       <c r="B17" s="28" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C17" s="27"/>
       <c r="D17" s="27">
-        <v>4357</v>
+        <v>580</v>
       </c>
       <c r="E17" s="28"/>
       <c r="F17" s="30">
@@ -1621,14 +1623,14 @@
     </row>
     <row r="18" spans="1:9" ht="15" customHeight="1">
       <c r="A18" s="27">
-        <v>2105</v>
+        <v>5000</v>
       </c>
       <c r="B18" s="28" t="s">
-        <v>25</v>
+        <v>91</v>
       </c>
       <c r="C18" s="27"/>
       <c r="D18" s="27">
-        <v>580</v>
+        <v>0</v>
       </c>
       <c r="E18" s="28"/>
       <c r="F18" s="27">
@@ -1644,14 +1646,14 @@
     </row>
     <row r="19" spans="1:9" ht="15" customHeight="1">
       <c r="A19" s="27">
-        <v>5000</v>
+        <v>4077</v>
       </c>
       <c r="B19" s="28" t="s">
-        <v>91</v>
+        <v>26</v>
       </c>
       <c r="C19" s="27"/>
       <c r="D19" s="27">
-        <v>0</v>
+        <v>2926</v>
       </c>
       <c r="E19" s="28"/>
       <c r="F19" s="27">
@@ -1667,14 +1669,14 @@
     </row>
     <row r="20" spans="1:9" ht="15" customHeight="1">
       <c r="A20" s="27">
-        <v>4077</v>
+        <v>230</v>
       </c>
       <c r="B20" s="28" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C20" s="27"/>
       <c r="D20" s="27">
-        <v>2926</v>
+        <v>30</v>
       </c>
       <c r="E20" s="28"/>
       <c r="F20" s="27">
@@ -1690,14 +1692,14 @@
     </row>
     <row r="21" spans="1:9" ht="15" customHeight="1">
       <c r="A21" s="27">
-        <v>230</v>
+        <v>826</v>
       </c>
       <c r="B21" s="28" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C21" s="27"/>
       <c r="D21" s="27">
-        <v>30</v>
+        <v>826</v>
       </c>
       <c r="E21" s="28"/>
       <c r="F21" s="27"/>
@@ -1707,14 +1709,14 @@
     </row>
     <row r="22" spans="1:9" ht="15" customHeight="1">
       <c r="A22" s="27">
-        <v>826</v>
+        <v>118000</v>
       </c>
       <c r="B22" s="28" t="s">
-        <v>28</v>
-      </c>
-      <c r="C22" s="27"/>
+        <v>93</v>
+      </c>
+      <c r="C22" s="28"/>
       <c r="D22" s="27">
-        <v>826</v>
+        <v>165000</v>
       </c>
       <c r="E22" s="28"/>
       <c r="F22" s="27"/>
@@ -1724,14 +1726,14 @@
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1">
       <c r="A23" s="27">
-        <v>118000</v>
+        <v>15000</v>
       </c>
       <c r="B23" s="28" t="s">
-        <v>93</v>
-      </c>
-      <c r="C23" s="28"/>
+        <v>94</v>
+      </c>
+      <c r="C23" s="27"/>
       <c r="D23" s="27">
-        <v>165000</v>
+        <v>0</v>
       </c>
       <c r="E23" s="28"/>
       <c r="F23" s="27"/>
@@ -1739,1084 +1741,1087 @@
       <c r="H23" s="27"/>
       <c r="I23" s="27"/>
     </row>
-    <row r="24" spans="1:9" ht="15" customHeight="1">
-      <c r="A24" s="27">
-        <v>15000</v>
-      </c>
-      <c r="B24" s="28" t="s">
-        <v>94</v>
-      </c>
+    <row r="24" spans="1:9">
+      <c r="A24" s="27"/>
+      <c r="B24" s="28"/>
       <c r="C24" s="27"/>
-      <c r="D24" s="27">
-        <v>0</v>
-      </c>
+      <c r="D24" s="27"/>
       <c r="E24" s="28"/>
       <c r="F24" s="27"/>
       <c r="G24" s="28"/>
       <c r="H24" s="27"/>
       <c r="I24" s="27"/>
     </row>
-    <row r="25" spans="1:9">
-      <c r="A25" s="27"/>
-      <c r="B25" s="28"/>
+    <row r="25" spans="1:9" ht="15" customHeight="1">
+      <c r="A25" s="27">
+        <v>20500</v>
+      </c>
+      <c r="B25" s="28" t="s">
+        <v>80</v>
+      </c>
       <c r="C25" s="27"/>
-      <c r="D25" s="27"/>
+      <c r="D25" s="27">
+        <f>I27-(SUM(D8:D23))</f>
+        <v>86740</v>
+      </c>
       <c r="E25" s="28"/>
-      <c r="F25" s="27"/>
-      <c r="G25" s="28"/>
+      <c r="F25" s="27">
+        <f>A27-(F18+F19+F20+F21+F22)</f>
+        <v>0</v>
+      </c>
+      <c r="G25" s="28" t="s">
+        <v>29</v>
+      </c>
       <c r="H25" s="27"/>
-      <c r="I25" s="27"/>
-    </row>
-    <row r="26" spans="1:9" ht="15" customHeight="1">
-      <c r="A26" s="27">
-        <f>F28-(A8+A9+A10+A11+A12+A13+A14+A15+A16+A17+A18+A19+A20+A21+A22+A23+A24)</f>
-        <v>20500</v>
-      </c>
-      <c r="B26" s="28" t="s">
-        <v>80</v>
-      </c>
+      <c r="I25" s="27">
+        <f>D27-(I18+I19+I20+I21+I22)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="10.050000000000001" customHeight="1">
+      <c r="A26" s="27"/>
+      <c r="B26" s="28"/>
       <c r="C26" s="27"/>
-      <c r="D26" s="27">
-        <f>I28-(D8+D9+D10+D11+D12+D13+D14+D15+D16+D17+D18+D19+D20+D21+D22+D23+D24)</f>
-        <v>70748</v>
-      </c>
+      <c r="D26" s="27"/>
       <c r="E26" s="28"/>
-      <c r="F26" s="27">
-        <f>A28-(F18+F19+F20+F21+F22)</f>
-        <v>0</v>
-      </c>
-      <c r="G26" s="28" t="s">
-        <v>29</v>
-      </c>
+      <c r="F26" s="27"/>
+      <c r="G26" s="28"/>
       <c r="H26" s="27"/>
-      <c r="I26" s="27">
-        <f>D28-(I18+I19+I20+I21+I22)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" ht="10.050000000000001" customHeight="1">
-      <c r="A27" s="27"/>
-      <c r="B27" s="28"/>
-      <c r="C27" s="27"/>
-      <c r="D27" s="27"/>
-      <c r="E27" s="28"/>
-      <c r="F27" s="27"/>
-      <c r="G27" s="28"/>
-      <c r="H27" s="27"/>
-      <c r="I27" s="27"/>
-    </row>
-    <row r="28" spans="1:9" s="33" customFormat="1" ht="19.95" customHeight="1" thickBot="1">
-      <c r="A28" s="31">
-        <f>SUM(A8:A26)</f>
+      <c r="I26" s="27"/>
+    </row>
+    <row r="27" spans="1:9" s="33" customFormat="1" ht="19.95" customHeight="1" thickBot="1">
+      <c r="A27" s="31">
+        <f>SUM(A8:A25)</f>
         <v>294436</v>
       </c>
-      <c r="B28" s="41" t="s">
-        <v>112</v>
-      </c>
-      <c r="C28" s="31"/>
-      <c r="D28" s="31">
-        <f>SUM(D8:D26)</f>
+      <c r="B27" s="41" t="s">
+        <v>111</v>
+      </c>
+      <c r="C27" s="31"/>
+      <c r="D27" s="31">
+        <f>SUM(D8:D25)</f>
         <v>396422</v>
       </c>
-      <c r="E28" s="32"/>
-      <c r="F28" s="31">
+      <c r="E27" s="32"/>
+      <c r="F27" s="31">
         <f>F18+F19+F20+F21</f>
         <v>294436</v>
       </c>
-      <c r="G28" s="41" t="s">
-        <v>112</v>
-      </c>
-      <c r="H28" s="31"/>
-      <c r="I28" s="31">
+      <c r="G27" s="41" t="s">
+        <v>111</v>
+      </c>
+      <c r="H27" s="31"/>
+      <c r="I27" s="31">
         <f>SUM(I18:I21)</f>
         <v>396422</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="8.1" customHeight="1" thickTop="1">
-      <c r="A29" s="20"/>
+    <row r="28" spans="1:9" ht="8.1" customHeight="1" thickTop="1">
+      <c r="A28" s="20"/>
+      <c r="I28" s="21"/>
+    </row>
+    <row r="29" spans="1:9" ht="14.4">
+      <c r="A29" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+      <c r="G29" s="19"/>
       <c r="I29" s="21"/>
     </row>
-    <row r="30" spans="1:9" ht="14.4">
-      <c r="A30" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="B30" s="11"/>
-      <c r="C30" s="11"/>
-      <c r="D30" s="11"/>
-      <c r="G30" s="19"/>
-      <c r="I30" s="21"/>
-    </row>
-    <row r="31" spans="1:9" ht="15.75" customHeight="1">
+    <row r="30" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A30" s="12"/>
+      <c r="B30" s="67"/>
+      <c r="C30" s="67"/>
+      <c r="D30" s="67"/>
+      <c r="G30" s="52" t="s">
+        <v>109</v>
+      </c>
+      <c r="H30" s="52"/>
+      <c r="I30" s="53"/>
+    </row>
+    <row r="31" spans="1:9" ht="14.4">
       <c r="A31" s="12"/>
-      <c r="B31" s="63"/>
-      <c r="C31" s="63"/>
-      <c r="D31" s="63"/>
-      <c r="G31" s="64" t="s">
-        <v>110</v>
-      </c>
-      <c r="H31" s="64"/>
-      <c r="I31" s="65"/>
+      <c r="B31" s="68"/>
+      <c r="C31" s="68"/>
+      <c r="D31" s="68"/>
+      <c r="G31" s="54"/>
+      <c r="H31" s="54"/>
+      <c r="I31" s="55"/>
     </row>
     <row r="32" spans="1:9" ht="14.4">
       <c r="A32" s="12"/>
-      <c r="B32" s="68"/>
-      <c r="C32" s="68"/>
-      <c r="D32" s="68"/>
-      <c r="G32" s="66"/>
-      <c r="H32" s="66"/>
-      <c r="I32" s="67"/>
+      <c r="B32" s="13"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="14"/>
+      <c r="F32" s="34"/>
+      <c r="G32" s="11"/>
+      <c r="H32" s="11"/>
+      <c r="I32" s="15"/>
     </row>
     <row r="33" spans="1:9" ht="14.4">
       <c r="A33" s="12"/>
       <c r="B33" s="13"/>
-      <c r="C33" s="13"/>
+      <c r="C33" s="35" t="s">
+        <v>104</v>
+      </c>
       <c r="D33" s="14"/>
-      <c r="F33" s="34"/>
       <c r="G33" s="11"/>
       <c r="H33" s="11"/>
       <c r="I33" s="15"/>
     </row>
     <row r="34" spans="1:9" ht="14.4">
-      <c r="A34" s="12"/>
+      <c r="A34" s="16" t="s">
+        <v>105</v>
+      </c>
       <c r="B34" s="13"/>
-      <c r="C34" s="35" t="s">
-        <v>105</v>
-      </c>
-      <c r="D34" s="14"/>
+      <c r="C34" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="D34" s="13"/>
       <c r="G34" s="11"/>
       <c r="H34" s="11"/>
       <c r="I34" s="15"/>
     </row>
     <row r="35" spans="1:9" ht="14.4">
-      <c r="A35" s="16" t="s">
-        <v>106</v>
-      </c>
-      <c r="B35" s="13"/>
+      <c r="A35" s="50">
+        <v>46234</v>
+      </c>
+      <c r="B35" s="51"/>
       <c r="C35" s="36" t="s">
         <v>107</v>
       </c>
-      <c r="D35" s="13"/>
-      <c r="G35" s="11"/>
-      <c r="H35" s="11"/>
-      <c r="I35" s="15"/>
-    </row>
-    <row r="36" spans="1:9" ht="14.4">
-      <c r="A36" s="50">
-        <v>46221</v>
-      </c>
-      <c r="B36" s="51"/>
-      <c r="C36" s="36" t="s">
+      <c r="D35" s="17"/>
+      <c r="G35" s="56" t="s">
         <v>108</v>
       </c>
-      <c r="D36" s="17"/>
-      <c r="G36" s="52" t="s">
-        <v>109</v>
-      </c>
-      <c r="H36" s="52"/>
-      <c r="I36" s="53"/>
-    </row>
-    <row r="37" spans="1:9" ht="7.95" customHeight="1">
-      <c r="A37" s="22"/>
-      <c r="B37" s="23"/>
-      <c r="C37" s="23"/>
-      <c r="D37" s="23"/>
-      <c r="E37" s="23"/>
-      <c r="F37" s="23"/>
-      <c r="G37" s="23"/>
-      <c r="H37" s="23"/>
-      <c r="I37" s="24"/>
-    </row>
-    <row r="43" spans="1:9" ht="19.95" customHeight="1">
-      <c r="A43" s="54" t="s">
+      <c r="H35" s="56"/>
+      <c r="I35" s="57"/>
+    </row>
+    <row r="36" spans="1:9" ht="7.95" customHeight="1">
+      <c r="A36" s="22"/>
+      <c r="B36" s="23"/>
+      <c r="C36" s="23"/>
+      <c r="D36" s="23"/>
+      <c r="E36" s="23"/>
+      <c r="F36" s="23"/>
+      <c r="G36" s="23"/>
+      <c r="H36" s="23"/>
+      <c r="I36" s="24"/>
+    </row>
+    <row r="37" spans="1:9" ht="7.95" customHeight="1"/>
+    <row r="39" spans="1:9" ht="19.95" customHeight="1">
+      <c r="A39" s="58" t="s">
         <v>0</v>
       </c>
-      <c r="B43" s="55"/>
-      <c r="C43" s="55"/>
-      <c r="D43" s="55"/>
-      <c r="E43" s="55"/>
-      <c r="F43" s="55"/>
-      <c r="G43" s="55"/>
-      <c r="H43" s="55"/>
-      <c r="I43" s="56"/>
-    </row>
-    <row r="44" spans="1:9" ht="14.4" customHeight="1">
-      <c r="A44" s="57" t="s">
+      <c r="B39" s="59"/>
+      <c r="C39" s="59"/>
+      <c r="D39" s="59"/>
+      <c r="E39" s="59"/>
+      <c r="F39" s="59"/>
+      <c r="G39" s="59"/>
+      <c r="H39" s="59"/>
+      <c r="I39" s="60"/>
+    </row>
+    <row r="40" spans="1:9" ht="14.4" customHeight="1">
+      <c r="A40" s="61" t="s">
         <v>78</v>
       </c>
-      <c r="B44" s="58"/>
-      <c r="C44" s="58"/>
-      <c r="D44" s="58"/>
-      <c r="E44" s="58"/>
-      <c r="F44" s="58"/>
-      <c r="G44" s="58"/>
-      <c r="H44" s="58"/>
-      <c r="I44" s="59"/>
-    </row>
-    <row r="45" spans="1:9" ht="19.95" customHeight="1">
-      <c r="A45" s="60" t="s">
-        <v>111</v>
-      </c>
-      <c r="B45" s="61"/>
-      <c r="C45" s="61"/>
-      <c r="D45" s="61"/>
-      <c r="E45" s="61"/>
-      <c r="F45" s="61"/>
-      <c r="G45" s="61"/>
-      <c r="H45" s="61"/>
-      <c r="I45" s="62"/>
-    </row>
-    <row r="46" spans="1:9" ht="19.95" customHeight="1" thickBot="1">
-      <c r="A46" s="25" t="s">
+      <c r="B40" s="62"/>
+      <c r="C40" s="62"/>
+      <c r="D40" s="62"/>
+      <c r="E40" s="62"/>
+      <c r="F40" s="62"/>
+      <c r="G40" s="62"/>
+      <c r="H40" s="62"/>
+      <c r="I40" s="63"/>
+    </row>
+    <row r="41" spans="1:9" ht="19.95" customHeight="1">
+      <c r="A41" s="64" t="s">
+        <v>110</v>
+      </c>
+      <c r="B41" s="65"/>
+      <c r="C41" s="65"/>
+      <c r="D41" s="65"/>
+      <c r="E41" s="65"/>
+      <c r="F41" s="65"/>
+      <c r="G41" s="65"/>
+      <c r="H41" s="65"/>
+      <c r="I41" s="66"/>
+    </row>
+    <row r="42" spans="1:9" ht="19.95" customHeight="1" thickBot="1">
+      <c r="A42" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B46" s="25" t="s">
+      <c r="B42" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="C46" s="26" t="s">
-        <v>103</v>
-      </c>
-      <c r="D46" s="26" t="s">
-        <v>103</v>
-      </c>
-      <c r="E46" s="25"/>
-      <c r="F46" s="25" t="s">
+      <c r="C42" s="26" t="s">
+        <v>102</v>
+      </c>
+      <c r="D42" s="26" t="s">
+        <v>102</v>
+      </c>
+      <c r="E42" s="25"/>
+      <c r="F42" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="G46" s="25" t="s">
+      <c r="G42" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="H46" s="26" t="s">
-        <v>103</v>
-      </c>
-      <c r="I46" s="26" t="s">
-        <v>103</v>
-      </c>
+      <c r="H42" s="26" t="s">
+        <v>102</v>
+      </c>
+      <c r="I42" s="26" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="15" customHeight="1">
+      <c r="A43" s="27"/>
+      <c r="B43" s="37" t="s">
+        <v>33</v>
+      </c>
+      <c r="C43" s="27"/>
+      <c r="D43" s="27"/>
+      <c r="E43" s="28"/>
+      <c r="F43" s="27"/>
+      <c r="G43" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="H43" s="27"/>
+      <c r="I43" s="27"/>
+    </row>
+    <row r="44" spans="1:9" ht="15" customHeight="1">
+      <c r="A44" s="27"/>
+      <c r="B44" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="C44" s="27"/>
+      <c r="D44" s="27"/>
+      <c r="E44" s="28"/>
+      <c r="F44" s="27">
+        <v>1521</v>
+      </c>
+      <c r="G44" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="H44" s="27">
+        <v>3697</v>
+      </c>
+      <c r="I44" s="27"/>
+    </row>
+    <row r="45" spans="1:9" ht="15" customHeight="1" thickBot="1">
+      <c r="A45" s="38">
+        <v>100000</v>
+      </c>
+      <c r="B45" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="C45" s="27"/>
+      <c r="D45" s="38">
+        <v>100000</v>
+      </c>
+      <c r="E45" s="28"/>
+      <c r="F45" s="27">
+        <v>42805.9</v>
+      </c>
+      <c r="G45" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="H45" s="30">
+        <v>159270.9</v>
+      </c>
+      <c r="I45" s="27">
+        <f>SUM(H44:H45)</f>
+        <v>162967.9</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="15" customHeight="1" thickTop="1">
+      <c r="A46" s="27"/>
+      <c r="B46" s="37" t="s">
+        <v>35</v>
+      </c>
+      <c r="C46" s="27"/>
+      <c r="D46" s="27"/>
+      <c r="E46" s="28"/>
+      <c r="F46" s="27"/>
+      <c r="G46" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="H46" s="27"/>
+      <c r="I46" s="27"/>
     </row>
     <row r="47" spans="1:9" ht="15" customHeight="1">
-      <c r="A47" s="27"/>
-      <c r="B47" s="37" t="s">
-        <v>33</v>
+      <c r="A47" s="27">
+        <v>3750</v>
+      </c>
+      <c r="B47" s="28" t="s">
+        <v>37</v>
       </c>
       <c r="C47" s="27"/>
-      <c r="D47" s="27"/>
+      <c r="D47" s="27">
+        <v>3750</v>
+      </c>
       <c r="E47" s="28"/>
-      <c r="F47" s="27"/>
-      <c r="G47" s="37" t="s">
-        <v>52</v>
-      </c>
-      <c r="H47" s="27"/>
-      <c r="I47" s="27"/>
+      <c r="F47" s="27">
+        <v>100</v>
+      </c>
+      <c r="G47" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="H47" s="28"/>
+      <c r="I47" s="27">
+        <v>100</v>
+      </c>
     </row>
     <row r="48" spans="1:9" ht="15" customHeight="1">
       <c r="A48" s="27"/>
-      <c r="B48" s="37" t="s">
-        <v>34</v>
+      <c r="B48" s="28" t="s">
+        <v>38</v>
       </c>
       <c r="C48" s="27"/>
       <c r="D48" s="27"/>
       <c r="E48" s="28"/>
-      <c r="F48" s="27">
-        <v>1521</v>
-      </c>
-      <c r="G48" s="28" t="s">
-        <v>53</v>
-      </c>
-      <c r="H48" s="27">
-        <v>3697</v>
-      </c>
+      <c r="F48" s="27"/>
+      <c r="G48" s="37" t="s">
+        <v>57</v>
+      </c>
+      <c r="H48" s="27"/>
       <c r="I48" s="27"/>
     </row>
-    <row r="49" spans="1:9" ht="15" customHeight="1" thickBot="1">
-      <c r="A49" s="38">
-        <v>100000</v>
-      </c>
-      <c r="B49" s="28" t="s">
-        <v>36</v>
+    <row r="49" spans="1:11" ht="15" customHeight="1">
+      <c r="A49" s="27"/>
+      <c r="B49" s="37" t="s">
+        <v>39</v>
       </c>
       <c r="C49" s="27"/>
-      <c r="D49" s="38">
-        <v>100000</v>
-      </c>
+      <c r="D49" s="27"/>
       <c r="E49" s="28"/>
       <c r="F49" s="27">
-        <v>42805.9</v>
+        <v>219225</v>
       </c>
       <c r="G49" s="28" t="s">
-        <v>54</v>
-      </c>
-      <c r="H49" s="30">
-        <v>159270.9</v>
-      </c>
-      <c r="I49" s="27">
-        <f>SUM(H48:H49)</f>
-        <v>162967.9</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" ht="15" customHeight="1" thickTop="1">
-      <c r="A50" s="27"/>
-      <c r="B50" s="37" t="s">
-        <v>35</v>
-      </c>
-      <c r="C50" s="27"/>
+        <v>41</v>
+      </c>
+      <c r="H49" s="27">
+        <v>219225</v>
+      </c>
+      <c r="I49" s="27"/>
+    </row>
+    <row r="50" spans="1:11" ht="15" customHeight="1">
+      <c r="A50" s="27">
+        <v>257956</v>
+      </c>
+      <c r="B50" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="C50" s="27">
+        <v>257956</v>
+      </c>
       <c r="D50" s="27"/>
       <c r="E50" s="28"/>
-      <c r="F50" s="27"/>
-      <c r="G50" s="37" t="s">
-        <v>55</v>
-      </c>
-      <c r="H50" s="27"/>
-      <c r="I50" s="27"/>
-    </row>
-    <row r="51" spans="1:9" ht="15" customHeight="1">
-      <c r="A51" s="27">
-        <v>3750</v>
-      </c>
+      <c r="F50" s="27">
+        <v>692085</v>
+      </c>
+      <c r="G50" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="H50" s="30">
+        <v>726065</v>
+      </c>
+      <c r="I50" s="27">
+        <f>SUM(H49:H50)</f>
+        <v>945290</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" ht="15" customHeight="1">
+      <c r="A51" s="27"/>
       <c r="B51" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="C51" s="27"/>
+        <v>89</v>
+      </c>
+      <c r="C51" s="30">
+        <v>51200</v>
+      </c>
       <c r="D51" s="27">
-        <v>3750</v>
+        <f>SUM(C50:C51)</f>
+        <v>309156</v>
       </c>
       <c r="E51" s="28"/>
-      <c r="F51" s="27">
-        <v>100</v>
-      </c>
-      <c r="G51" s="28" t="s">
-        <v>56</v>
-      </c>
-      <c r="H51" s="28"/>
-      <c r="I51" s="27">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" ht="15" customHeight="1">
+      <c r="F51" s="27"/>
+      <c r="G51" s="37" t="s">
+        <v>59</v>
+      </c>
+      <c r="H51" s="27"/>
+      <c r="I51" s="27"/>
+    </row>
+    <row r="52" spans="1:11" ht="15" customHeight="1">
       <c r="A52" s="27"/>
-      <c r="B52" s="28" t="s">
-        <v>38</v>
+      <c r="B52" s="37" t="s">
+        <v>41</v>
       </c>
       <c r="C52" s="27"/>
       <c r="D52" s="27"/>
       <c r="E52" s="28"/>
-      <c r="F52" s="27"/>
-      <c r="G52" s="37" t="s">
-        <v>57</v>
-      </c>
-      <c r="H52" s="27"/>
+      <c r="F52" s="27">
+        <v>21489</v>
+      </c>
+      <c r="G52" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="H52" s="27">
+        <v>36034</v>
+      </c>
       <c r="I52" s="27"/>
     </row>
-    <row r="53" spans="1:9" ht="15" customHeight="1">
-      <c r="A53" s="27"/>
-      <c r="B53" s="37" t="s">
-        <v>39</v>
-      </c>
-      <c r="C53" s="27"/>
+    <row r="53" spans="1:11" ht="15" customHeight="1">
+      <c r="A53" s="27">
+        <v>333039</v>
+      </c>
+      <c r="B53" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="C53" s="27">
+        <v>333039</v>
+      </c>
       <c r="D53" s="27"/>
       <c r="E53" s="28"/>
       <c r="F53" s="27">
-        <v>219225</v>
+        <v>43095</v>
       </c>
       <c r="G53" s="28" t="s">
-        <v>41</v>
-      </c>
-      <c r="H53" s="27">
-        <v>219225</v>
-      </c>
-      <c r="I53" s="27"/>
-    </row>
-    <row r="54" spans="1:9" ht="15" customHeight="1">
-      <c r="A54" s="27">
-        <v>257956</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="H53" s="30">
+        <v>53843</v>
+      </c>
+      <c r="I53" s="27">
+        <f>SUM(H52:H53)</f>
+        <v>89877</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" ht="15" customHeight="1">
+      <c r="A54" s="27"/>
       <c r="B54" s="28" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C54" s="27">
-        <v>257956</v>
+        <v>1464</v>
       </c>
       <c r="D54" s="27"/>
       <c r="E54" s="28"/>
-      <c r="F54" s="27">
-        <v>692085</v>
-      </c>
-      <c r="G54" s="28" t="s">
-        <v>58</v>
-      </c>
-      <c r="H54" s="30">
-        <v>726065</v>
-      </c>
-      <c r="I54" s="27">
-        <f>SUM(H53:H54)</f>
-        <v>945290</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" ht="15" customHeight="1">
+      <c r="F54" s="27"/>
+      <c r="G54" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="H54" s="27"/>
+      <c r="I54" s="27"/>
+    </row>
+    <row r="55" spans="1:11" ht="15" customHeight="1">
       <c r="A55" s="27"/>
       <c r="B55" s="28" t="s">
-        <v>89</v>
+        <v>43</v>
       </c>
       <c r="C55" s="30">
-        <v>51200</v>
+        <v>16753</v>
       </c>
       <c r="D55" s="27">
-        <f>SUM(C54:C55)</f>
-        <v>309156</v>
+        <f>SUM(C53:C55)</f>
+        <v>351256</v>
       </c>
       <c r="E55" s="28"/>
-      <c r="F55" s="27"/>
-      <c r="G55" s="37" t="s">
-        <v>59</v>
+      <c r="F55" s="27">
+        <v>208101</v>
+      </c>
+      <c r="G55" s="28" t="s">
+        <v>61</v>
       </c>
       <c r="H55" s="27"/>
-      <c r="I55" s="27"/>
-    </row>
-    <row r="56" spans="1:9" ht="15" customHeight="1">
+      <c r="I55" s="27">
+        <v>345990</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" ht="15" customHeight="1">
       <c r="A56" s="27"/>
       <c r="B56" s="37" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C56" s="27"/>
       <c r="D56" s="27"/>
       <c r="E56" s="28"/>
-      <c r="F56" s="27">
-        <v>21489</v>
-      </c>
-      <c r="G56" s="28" t="s">
-        <v>41</v>
-      </c>
-      <c r="H56" s="27">
-        <v>36034</v>
-      </c>
-      <c r="I56" s="27"/>
-    </row>
-    <row r="57" spans="1:9" ht="15" customHeight="1">
+      <c r="F56" s="28"/>
+      <c r="G56" s="28"/>
+      <c r="H56" s="28"/>
+      <c r="I56" s="28"/>
+    </row>
+    <row r="57" spans="1:11" ht="15" customHeight="1">
       <c r="A57" s="27">
-        <v>333039</v>
+        <v>66010</v>
       </c>
       <c r="B57" s="28" t="s">
         <v>40</v>
       </c>
       <c r="C57" s="27">
-        <v>333039</v>
+        <v>66010</v>
       </c>
       <c r="D57" s="27"/>
       <c r="E57" s="28"/>
-      <c r="F57" s="27">
-        <v>43095</v>
-      </c>
-      <c r="G57" s="28" t="s">
-        <v>58</v>
-      </c>
-      <c r="H57" s="30">
-        <v>53843</v>
-      </c>
-      <c r="I57" s="27">
-        <f>SUM(H56:H57)</f>
-        <v>89877</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" ht="15" customHeight="1">
+      <c r="F57" s="27"/>
+      <c r="G57" s="37" t="s">
+        <v>87</v>
+      </c>
+      <c r="H57" s="27"/>
+      <c r="I57" s="27"/>
+    </row>
+    <row r="58" spans="1:11" ht="15" customHeight="1">
       <c r="A58" s="27"/>
       <c r="B58" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="C58" s="27">
-        <v>1464</v>
-      </c>
-      <c r="D58" s="27"/>
+      <c r="C58" s="30">
+        <v>5400</v>
+      </c>
+      <c r="D58" s="27">
+        <f>SUM(C57:C58)</f>
+        <v>71410</v>
+      </c>
       <c r="E58" s="28"/>
-      <c r="F58" s="27"/>
-      <c r="G58" s="37" t="s">
-        <v>60</v>
+      <c r="F58" s="27">
+        <v>1970</v>
+      </c>
+      <c r="G58" s="28" t="s">
+        <v>88</v>
       </c>
       <c r="H58" s="27"/>
-      <c r="I58" s="27"/>
-    </row>
-    <row r="59" spans="1:9" ht="15" customHeight="1">
+      <c r="I58" s="27">
+        <v>1970</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" ht="15" customHeight="1">
       <c r="A59" s="27"/>
-      <c r="B59" s="28" t="s">
-        <v>43</v>
-      </c>
-      <c r="C59" s="30">
-        <v>16753</v>
-      </c>
-      <c r="D59" s="27">
-        <f>SUM(C57:C59)</f>
-        <v>351256</v>
-      </c>
+      <c r="B59" s="37" t="s">
+        <v>64</v>
+      </c>
+      <c r="C59" s="27"/>
+      <c r="D59" s="27"/>
       <c r="E59" s="28"/>
       <c r="F59" s="27">
-        <v>208101</v>
+        <v>4230</v>
       </c>
       <c r="G59" s="28" t="s">
-        <v>61</v>
-      </c>
-      <c r="H59" s="27"/>
+        <v>90</v>
+      </c>
+      <c r="H59" s="28"/>
       <c r="I59" s="27">
-        <v>345990</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" ht="15" customHeight="1">
-      <c r="A60" s="27"/>
-      <c r="B60" s="37" t="s">
-        <v>44</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" ht="15" customHeight="1">
+      <c r="A60" s="27">
+        <v>35882</v>
+      </c>
+      <c r="B60" s="28" t="s">
+        <v>40</v>
       </c>
       <c r="C60" s="27"/>
-      <c r="D60" s="27"/>
+      <c r="D60" s="27">
+        <v>35882</v>
+      </c>
       <c r="E60" s="28"/>
-      <c r="F60" s="28"/>
-      <c r="G60" s="28"/>
+      <c r="F60" s="27">
+        <v>4804</v>
+      </c>
+      <c r="G60" s="28" t="s">
+        <v>92</v>
+      </c>
       <c r="H60" s="28"/>
-      <c r="I60" s="28"/>
-    </row>
-    <row r="61" spans="1:9" ht="15" customHeight="1">
-      <c r="A61" s="27">
-        <v>66010</v>
-      </c>
-      <c r="B61" s="28" t="s">
-        <v>40</v>
-      </c>
-      <c r="C61" s="27">
-        <v>66010</v>
-      </c>
-      <c r="D61" s="27"/>
+      <c r="I60" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" ht="15" customHeight="1">
+      <c r="A61" s="28"/>
+      <c r="B61" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="C61" s="28"/>
+      <c r="D61" s="28"/>
       <c r="E61" s="28"/>
-      <c r="F61" s="27"/>
-      <c r="G61" s="37" t="s">
-        <v>87</v>
+      <c r="F61" s="27">
+        <v>6958</v>
+      </c>
+      <c r="G61" s="28" t="s">
+        <v>95</v>
       </c>
       <c r="H61" s="27"/>
-      <c r="I61" s="27"/>
-    </row>
-    <row r="62" spans="1:9" ht="15" customHeight="1">
-      <c r="A62" s="27"/>
+      <c r="I61" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" ht="15" customHeight="1">
+      <c r="A62" s="27">
+        <v>50</v>
+      </c>
       <c r="B62" s="28" t="s">
-        <v>42</v>
-      </c>
-      <c r="C62" s="30">
-        <v>5400</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="C62" s="27"/>
       <c r="D62" s="27">
-        <f>SUM(C61:C62)</f>
-        <v>71410</v>
+        <v>3401</v>
       </c>
       <c r="E62" s="28"/>
       <c r="F62" s="27">
-        <v>1970</v>
+        <v>0</v>
       </c>
       <c r="G62" s="28" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="H62" s="27"/>
       <c r="I62" s="27">
-        <v>1970</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" ht="15" customHeight="1">
-      <c r="A63" s="27"/>
-      <c r="B63" s="37" t="s">
-        <v>64</v>
+        <v>6586</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" ht="15" customHeight="1">
+      <c r="A63" s="27">
+        <v>250000</v>
+      </c>
+      <c r="B63" s="28" t="s">
+        <v>65</v>
       </c>
       <c r="C63" s="27"/>
-      <c r="D63" s="27"/>
+      <c r="D63" s="27">
+        <v>250000</v>
+      </c>
       <c r="E63" s="28"/>
-      <c r="F63" s="27">
-        <v>4230</v>
-      </c>
-      <c r="G63" s="28" t="s">
-        <v>90</v>
-      </c>
-      <c r="H63" s="28"/>
-      <c r="I63" s="27">
+      <c r="F63" s="27"/>
+      <c r="G63" s="37"/>
+      <c r="H63" s="27"/>
+      <c r="I63" s="27"/>
+    </row>
+    <row r="64" spans="1:11" ht="15" customHeight="1">
+      <c r="A64" s="27">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="1:9" ht="15" customHeight="1">
-      <c r="A64" s="27">
-        <v>35882</v>
-      </c>
       <c r="B64" s="28" t="s">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="C64" s="27"/>
       <c r="D64" s="27">
-        <v>35882</v>
+        <v>150000</v>
       </c>
       <c r="E64" s="28"/>
-      <c r="F64" s="27">
-        <v>4804</v>
-      </c>
-      <c r="G64" s="28" t="s">
-        <v>92</v>
-      </c>
-      <c r="H64" s="28"/>
-      <c r="I64" s="27">
-        <v>0</v>
-      </c>
+      <c r="F64" s="27"/>
+      <c r="G64" s="28"/>
+      <c r="H64" s="27"/>
+      <c r="I64" s="27"/>
+      <c r="K64" s="39"/>
     </row>
     <row r="65" spans="1:11" ht="15" customHeight="1">
-      <c r="A65" s="28"/>
+      <c r="A65" s="27"/>
       <c r="B65" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="C65" s="28"/>
-      <c r="D65" s="28"/>
+        <v>46</v>
+      </c>
+      <c r="C65" s="27"/>
+      <c r="D65" s="27"/>
       <c r="E65" s="28"/>
-      <c r="F65" s="27">
-        <v>6958</v>
-      </c>
-      <c r="G65" s="28" t="s">
-        <v>95</v>
+      <c r="F65" s="27"/>
+      <c r="G65" s="37" t="s">
+        <v>62</v>
       </c>
       <c r="H65" s="27"/>
-      <c r="I65" s="27">
-        <v>0</v>
-      </c>
+      <c r="I65" s="27"/>
     </row>
     <row r="66" spans="1:11" ht="15" customHeight="1">
       <c r="A66" s="27">
-        <v>50</v>
+        <v>1500</v>
       </c>
       <c r="B66" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="C66" s="27"/>
-      <c r="D66" s="27">
-        <v>3401</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="C66" s="27">
+        <v>1800</v>
+      </c>
+      <c r="D66" s="27"/>
       <c r="E66" s="28"/>
       <c r="F66" s="27">
-        <v>0</v>
+        <v>16623</v>
       </c>
       <c r="G66" s="28" t="s">
-        <v>100</v>
-      </c>
-      <c r="H66" s="27"/>
-      <c r="I66" s="27">
-        <v>6586</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="H66" s="27">
+        <v>16623</v>
+      </c>
+      <c r="I66" s="27"/>
     </row>
     <row r="67" spans="1:11" ht="15" customHeight="1">
       <c r="A67" s="27">
-        <v>250000</v>
+        <v>1500</v>
       </c>
       <c r="B67" s="28" t="s">
-        <v>65</v>
-      </c>
-      <c r="C67" s="27"/>
-      <c r="D67" s="27">
-        <v>250000</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="C67" s="27">
+        <v>3000</v>
+      </c>
+      <c r="D67" s="27"/>
       <c r="E67" s="28"/>
-      <c r="F67" s="27"/>
-      <c r="G67" s="37"/>
-      <c r="H67" s="27"/>
-      <c r="I67" s="27"/>
+      <c r="F67" s="28"/>
+      <c r="G67" s="28" t="s">
+        <v>81</v>
+      </c>
+      <c r="H67" s="27">
+        <v>0</v>
+      </c>
+      <c r="I67" s="28"/>
     </row>
     <row r="68" spans="1:11" ht="15" customHeight="1">
-      <c r="A68" s="27"/>
+      <c r="A68" s="27">
+        <v>3500</v>
+      </c>
       <c r="B68" s="28" t="s">
-        <v>101</v>
-      </c>
-      <c r="C68" s="27"/>
-      <c r="D68" s="27">
-        <v>150000</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="C68" s="27">
+        <v>3500</v>
+      </c>
+      <c r="D68" s="27"/>
       <c r="E68" s="28"/>
       <c r="F68" s="27"/>
-      <c r="G68" s="28"/>
-      <c r="H68" s="27"/>
-      <c r="I68" s="27"/>
-      <c r="K68" s="39"/>
+      <c r="G68" s="28" t="s">
+        <v>63</v>
+      </c>
+      <c r="H68" s="30">
+        <v>-2493</v>
+      </c>
+      <c r="I68" s="27">
+        <f>SUM(H66:H68)</f>
+        <v>14130</v>
+      </c>
     </row>
     <row r="69" spans="1:11" ht="15" customHeight="1">
-      <c r="A69" s="27"/>
-      <c r="B69" s="37" t="s">
-        <v>46</v>
-      </c>
-      <c r="C69" s="27"/>
+      <c r="A69" s="27">
+        <v>10532</v>
+      </c>
+      <c r="B69" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="C69" s="27">
+        <v>11000</v>
+      </c>
       <c r="D69" s="27"/>
       <c r="E69" s="28"/>
       <c r="F69" s="27"/>
-      <c r="G69" s="37" t="s">
-        <v>62</v>
-      </c>
+      <c r="G69" s="28"/>
       <c r="H69" s="27"/>
       <c r="I69" s="27"/>
     </row>
     <row r="70" spans="1:11" ht="15" customHeight="1">
       <c r="A70" s="27">
-        <v>1500</v>
+        <v>1880</v>
       </c>
       <c r="B70" s="28" t="s">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="C70" s="27">
-        <v>1800</v>
+        <v>1910</v>
       </c>
       <c r="D70" s="27"/>
       <c r="E70" s="28"/>
       <c r="F70" s="27">
-        <v>16623</v>
-      </c>
-      <c r="G70" s="28" t="s">
-        <v>40</v>
-      </c>
-      <c r="H70" s="27">
-        <v>16623</v>
-      </c>
-      <c r="I70" s="27"/>
+        <v>12425</v>
+      </c>
+      <c r="G70" s="37" t="s">
+        <v>82</v>
+      </c>
+      <c r="H70" s="28"/>
+      <c r="I70" s="28"/>
     </row>
     <row r="71" spans="1:11" ht="15" customHeight="1">
       <c r="A71" s="27">
-        <v>1500</v>
-      </c>
-      <c r="B71" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="C71" s="27">
-        <v>3000</v>
-      </c>
-      <c r="D71" s="27"/>
+        <v>4630</v>
+      </c>
+      <c r="B71" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="C71" s="30">
+        <v>5456</v>
+      </c>
+      <c r="D71" s="40">
+        <f>SUM(C66:C71)</f>
+        <v>26666</v>
+      </c>
       <c r="E71" s="28"/>
       <c r="F71" s="28"/>
       <c r="G71" s="28" t="s">
-        <v>81</v>
+        <v>40</v>
       </c>
       <c r="H71" s="27">
-        <v>0</v>
+        <v>12425</v>
       </c>
       <c r="I71" s="28"/>
+      <c r="K71" s="39"/>
     </row>
     <row r="72" spans="1:11" ht="15" customHeight="1">
-      <c r="A72" s="27">
-        <v>3500</v>
-      </c>
-      <c r="B72" s="28" t="s">
-        <v>49</v>
-      </c>
-      <c r="C72" s="27">
-        <v>3500</v>
-      </c>
-      <c r="D72" s="27"/>
+      <c r="A72" s="28"/>
+      <c r="B72" s="28"/>
+      <c r="C72" s="28"/>
+      <c r="D72" s="40"/>
       <c r="E72" s="28"/>
       <c r="F72" s="27"/>
       <c r="G72" s="28" t="s">
         <v>63</v>
       </c>
       <c r="H72" s="30">
-        <v>-2493</v>
-      </c>
-      <c r="I72" s="27">
-        <f>SUM(H70:H72)</f>
-        <v>14130</v>
-      </c>
+        <v>-1864</v>
+      </c>
+      <c r="I72" s="28"/>
     </row>
     <row r="73" spans="1:11" ht="15" customHeight="1">
       <c r="A73" s="27">
-        <v>10532</v>
-      </c>
-      <c r="B73" s="28" t="s">
-        <v>5</v>
-      </c>
-      <c r="C73" s="27">
-        <v>11000</v>
-      </c>
+        <v>305202.90000000002</v>
+      </c>
+      <c r="B73" s="37" t="s">
+        <v>51</v>
+      </c>
+      <c r="C73" s="27"/>
       <c r="D73" s="27"/>
       <c r="E73" s="28"/>
-      <c r="F73" s="27"/>
+      <c r="F73" s="28"/>
       <c r="G73" s="28"/>
       <c r="H73" s="27"/>
-      <c r="I73" s="27"/>
+      <c r="I73" s="27">
+        <f>SUM(H71:H72)</f>
+        <v>10561</v>
+      </c>
     </row>
     <row r="74" spans="1:11" ht="15" customHeight="1">
-      <c r="A74" s="27">
-        <v>1880</v>
-      </c>
+      <c r="A74" s="27"/>
       <c r="B74" s="28" t="s">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="C74" s="27">
-        <v>1910</v>
-      </c>
-      <c r="D74" s="27"/>
+        <v>305202.90000000002</v>
+      </c>
+      <c r="D74" s="40"/>
       <c r="E74" s="28"/>
-      <c r="F74" s="27">
-        <v>12425</v>
-      </c>
-      <c r="G74" s="37" t="s">
-        <v>82</v>
-      </c>
-      <c r="H74" s="28"/>
-      <c r="I74" s="28"/>
+      <c r="F74" s="27"/>
+      <c r="G74" s="28"/>
+      <c r="H74" s="27"/>
+      <c r="I74" s="27"/>
     </row>
     <row r="75" spans="1:11" ht="15" customHeight="1">
-      <c r="A75" s="27">
-        <v>4630</v>
-      </c>
-      <c r="B75" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="C75" s="30">
-        <v>5456</v>
-      </c>
-      <c r="D75" s="40">
-        <f>SUM(C70:C75)</f>
-        <v>26666</v>
-      </c>
+      <c r="A75" s="27"/>
+      <c r="B75" s="28" t="s">
+        <v>112</v>
+      </c>
+      <c r="C75" s="27">
+        <v>15992</v>
+      </c>
+      <c r="D75" s="40"/>
       <c r="E75" s="28"/>
-      <c r="F75" s="28"/>
-      <c r="G75" s="28" t="s">
-        <v>40</v>
-      </c>
-      <c r="H75" s="27">
-        <v>12425</v>
-      </c>
-      <c r="I75" s="28"/>
-      <c r="K75" s="39"/>
+      <c r="F75" s="27"/>
+      <c r="G75" s="28"/>
+      <c r="H75" s="27"/>
+      <c r="I75" s="27"/>
     </row>
     <row r="76" spans="1:11" ht="15" customHeight="1">
-      <c r="A76" s="28"/>
-      <c r="B76" s="28"/>
-      <c r="C76" s="28"/>
-      <c r="D76" s="40"/>
+      <c r="A76" s="27"/>
+      <c r="B76" s="28" t="s">
+        <v>84</v>
+      </c>
+      <c r="C76" s="27">
+        <f>D25</f>
+        <v>86740</v>
+      </c>
+      <c r="D76" s="27">
+        <f>+C74-C75+C76</f>
+        <v>375950.9</v>
+      </c>
       <c r="E76" s="28"/>
       <c r="F76" s="27"/>
-      <c r="G76" s="28" t="s">
-        <v>63</v>
-      </c>
-      <c r="H76" s="30">
-        <v>-1864</v>
-      </c>
-      <c r="I76" s="28"/>
-    </row>
-    <row r="77" spans="1:11" ht="15" customHeight="1">
-      <c r="A77" s="27">
-        <v>305202.90000000002</v>
-      </c>
-      <c r="B77" s="37" t="s">
-        <v>51</v>
-      </c>
-      <c r="C77" s="27"/>
-      <c r="D77" s="27"/>
-      <c r="E77" s="28"/>
-      <c r="F77" s="28"/>
-      <c r="G77" s="28"/>
-      <c r="H77" s="27"/>
-      <c r="I77" s="27">
-        <f>SUM(H75:H76)</f>
-        <v>10561</v>
-      </c>
-    </row>
-    <row r="78" spans="1:11" ht="15" customHeight="1">
-      <c r="A78" s="27"/>
-      <c r="B78" s="28" t="s">
-        <v>40</v>
-      </c>
-      <c r="C78" s="27">
-        <v>305202.90000000002</v>
-      </c>
-      <c r="D78" s="40"/>
-      <c r="E78" s="28"/>
-      <c r="F78" s="27"/>
-      <c r="G78" s="28"/>
-      <c r="H78" s="27"/>
-      <c r="I78" s="27"/>
-    </row>
-    <row r="79" spans="1:11" ht="15" customHeight="1">
-      <c r="A79" s="27"/>
-      <c r="B79" s="28" t="s">
-        <v>84</v>
-      </c>
-      <c r="C79" s="27">
-        <f>D26</f>
-        <v>70748</v>
-      </c>
-      <c r="D79" s="27">
-        <f>SUM(C78:C79)</f>
-        <v>375950.9</v>
-      </c>
-      <c r="E79" s="28"/>
-      <c r="F79" s="27"/>
-      <c r="G79" s="28"/>
-      <c r="H79" s="27"/>
-      <c r="I79" s="27"/>
-    </row>
-    <row r="80" spans="1:11" s="33" customFormat="1" ht="19.95" customHeight="1" thickBot="1">
-      <c r="A80" s="31">
-        <f>SUM(A51:A79)</f>
+      <c r="G76" s="28"/>
+      <c r="H76" s="27"/>
+      <c r="I76" s="27"/>
+    </row>
+    <row r="77" spans="1:11" s="33" customFormat="1" ht="19.95" customHeight="1" thickBot="1">
+      <c r="A77" s="31">
+        <f>SUM(A47:A76)</f>
         <v>1275431.8999999999</v>
       </c>
-      <c r="B80" s="41" t="s">
-        <v>112</v>
-      </c>
-      <c r="C80" s="31"/>
-      <c r="D80" s="31">
-        <f>SUM(D51:D79)</f>
+      <c r="B77" s="41" t="s">
+        <v>111</v>
+      </c>
+      <c r="C77" s="31"/>
+      <c r="D77" s="31">
+        <f>SUM(D47:D76)</f>
         <v>1577471.9</v>
       </c>
-      <c r="E80" s="32"/>
-      <c r="F80" s="31">
-        <f>SUM(F47:F79)</f>
+      <c r="E77" s="32"/>
+      <c r="F77" s="31">
+        <f>SUM(F43:F76)</f>
         <v>1275431.8999999999</v>
       </c>
-      <c r="G80" s="41" t="s">
-        <v>112</v>
-      </c>
-      <c r="H80" s="31"/>
-      <c r="I80" s="31">
-        <f>SUM(I47:I79)</f>
+      <c r="G77" s="41" t="s">
+        <v>111</v>
+      </c>
+      <c r="H77" s="31"/>
+      <c r="I77" s="31">
+        <f>SUM(I43:I76)</f>
         <v>1577471.9</v>
       </c>
     </row>
-    <row r="81" spans="1:9" ht="8.1" customHeight="1" thickTop="1">
-      <c r="A81" s="20"/>
-      <c r="I81" s="21"/>
+    <row r="78" spans="1:11" ht="8.1" customHeight="1" thickTop="1">
+      <c r="A78" s="20"/>
+      <c r="I78" s="21"/>
+    </row>
+    <row r="79" spans="1:11" ht="14.4">
+      <c r="A79" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="B79" s="11"/>
+      <c r="C79" s="11"/>
+      <c r="D79" s="11"/>
+      <c r="G79" s="19"/>
+      <c r="I79" s="21"/>
+    </row>
+    <row r="80" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A80" s="12"/>
+      <c r="B80" s="67"/>
+      <c r="C80" s="67"/>
+      <c r="D80" s="67"/>
+      <c r="G80" s="52" t="s">
+        <v>109</v>
+      </c>
+      <c r="H80" s="52"/>
+      <c r="I80" s="53"/>
+    </row>
+    <row r="81" spans="1:9" ht="14.4">
+      <c r="A81" s="12"/>
+      <c r="B81" s="68"/>
+      <c r="C81" s="68"/>
+      <c r="D81" s="68"/>
+      <c r="G81" s="54"/>
+      <c r="H81" s="54"/>
+      <c r="I81" s="55"/>
     </row>
     <row r="82" spans="1:9" ht="14.4">
-      <c r="A82" s="10" t="s">
+      <c r="A82" s="12"/>
+      <c r="B82" s="13"/>
+      <c r="C82" s="13"/>
+      <c r="D82" s="14"/>
+      <c r="F82" s="34"/>
+      <c r="G82" s="11"/>
+      <c r="H82" s="11"/>
+      <c r="I82" s="15"/>
+    </row>
+    <row r="83" spans="1:9" ht="14.4">
+      <c r="A83" s="12"/>
+      <c r="B83" s="13"/>
+      <c r="C83" s="35" t="s">
         <v>104</v>
       </c>
-      <c r="B82" s="11"/>
-      <c r="C82" s="11"/>
-      <c r="D82" s="11"/>
-      <c r="G82" s="19"/>
-      <c r="I82" s="21"/>
-    </row>
-    <row r="83" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A83" s="12"/>
-      <c r="B83" s="63"/>
-      <c r="C83" s="63"/>
-      <c r="D83" s="63"/>
-      <c r="G83" s="64" t="s">
-        <v>110</v>
-      </c>
-      <c r="H83" s="64"/>
-      <c r="I83" s="65"/>
+      <c r="D83" s="14"/>
+      <c r="G83" s="11"/>
+      <c r="H83" s="11"/>
+      <c r="I83" s="15"/>
     </row>
     <row r="84" spans="1:9" ht="14.4">
-      <c r="A84" s="12"/>
-      <c r="B84" s="68"/>
-      <c r="C84" s="68"/>
-      <c r="D84" s="68"/>
-      <c r="G84" s="66"/>
-      <c r="H84" s="66"/>
-      <c r="I84" s="67"/>
+      <c r="A84" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="B84" s="13"/>
+      <c r="C84" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="D84" s="13"/>
+      <c r="G84" s="11"/>
+      <c r="H84" s="11"/>
+      <c r="I84" s="15"/>
     </row>
     <row r="85" spans="1:9" ht="14.4">
-      <c r="A85" s="12"/>
-      <c r="B85" s="13"/>
-      <c r="C85" s="13"/>
-      <c r="D85" s="14"/>
-      <c r="F85" s="34"/>
-      <c r="G85" s="11"/>
-      <c r="H85" s="11"/>
-      <c r="I85" s="15"/>
-    </row>
-    <row r="86" spans="1:9" ht="14.4">
-      <c r="A86" s="12"/>
-      <c r="B86" s="13"/>
-      <c r="C86" s="35" t="s">
-        <v>105</v>
-      </c>
-      <c r="D86" s="14"/>
-      <c r="G86" s="11"/>
-      <c r="H86" s="11"/>
-      <c r="I86" s="15"/>
-    </row>
-    <row r="87" spans="1:9" ht="14.4">
-      <c r="A87" s="16" t="s">
-        <v>106</v>
-      </c>
-      <c r="B87" s="13"/>
-      <c r="C87" s="36" t="s">
+      <c r="A85" s="50">
+        <v>46234</v>
+      </c>
+      <c r="B85" s="51"/>
+      <c r="C85" s="36" t="s">
         <v>107</v>
       </c>
-      <c r="D87" s="13"/>
-      <c r="G87" s="11"/>
-      <c r="H87" s="11"/>
-      <c r="I87" s="15"/>
-    </row>
-    <row r="88" spans="1:9" ht="14.4">
-      <c r="A88" s="50">
-        <v>46221</v>
-      </c>
-      <c r="B88" s="51"/>
-      <c r="C88" s="36" t="s">
+      <c r="D85" s="17"/>
+      <c r="G85" s="56" t="s">
         <v>108</v>
       </c>
-      <c r="D88" s="17"/>
-      <c r="G88" s="52" t="s">
-        <v>109</v>
-      </c>
-      <c r="H88" s="52"/>
-      <c r="I88" s="53"/>
-    </row>
-    <row r="89" spans="1:9" ht="7.95" customHeight="1">
-      <c r="A89" s="22"/>
-      <c r="B89" s="23"/>
-      <c r="C89" s="23"/>
-      <c r="D89" s="23"/>
-      <c r="E89" s="23"/>
-      <c r="F89" s="23"/>
-      <c r="G89" s="23"/>
-      <c r="H89" s="23"/>
-      <c r="I89" s="24"/>
-    </row>
-    <row r="90" spans="1:9">
-      <c r="A90" s="40"/>
-      <c r="C90" s="40"/>
-      <c r="D90" s="40"/>
-      <c r="F90" s="40"/>
-      <c r="H90" s="40"/>
-      <c r="I90" s="40"/>
-    </row>
-    <row r="91" spans="1:9">
-      <c r="A91" s="40"/>
-      <c r="C91" s="40"/>
-      <c r="D91" s="40"/>
-      <c r="F91" s="40"/>
-      <c r="H91" s="40"/>
-      <c r="I91" s="40"/>
-    </row>
-    <row r="92" spans="1:9">
-      <c r="A92" s="40"/>
-      <c r="C92" s="40"/>
-      <c r="D92" s="40"/>
-      <c r="F92" s="40"/>
-      <c r="H92" s="40"/>
-      <c r="I92" s="40"/>
+      <c r="H85" s="56"/>
+      <c r="I85" s="57"/>
+    </row>
+    <row r="86" spans="1:9" ht="7.95" customHeight="1">
+      <c r="A86" s="22"/>
+      <c r="B86" s="23"/>
+      <c r="C86" s="23"/>
+      <c r="D86" s="23"/>
+      <c r="E86" s="23"/>
+      <c r="F86" s="23"/>
+      <c r="G86" s="23"/>
+      <c r="H86" s="23"/>
+      <c r="I86" s="24"/>
+    </row>
+    <row r="87" spans="1:9">
+      <c r="A87" s="40"/>
+      <c r="C87" s="40"/>
+      <c r="D87" s="40"/>
+      <c r="F87" s="40"/>
+      <c r="H87" s="40"/>
+      <c r="I87" s="40"/>
+    </row>
+    <row r="88" spans="1:9">
+      <c r="A88" s="40"/>
+      <c r="C88" s="40"/>
+      <c r="D88" s="40"/>
+      <c r="F88" s="40"/>
+      <c r="H88" s="40"/>
+      <c r="I88" s="40"/>
+    </row>
+    <row r="89" spans="1:9">
+      <c r="A89" s="40"/>
+      <c r="C89" s="40"/>
+      <c r="D89" s="40"/>
+      <c r="F89" s="40"/>
+      <c r="H89" s="40"/>
+      <c r="I89" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="16">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="A4:I4"/>
+    <mergeCell ref="B30:D30"/>
     <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="G31:I32"/>
-    <mergeCell ref="G36:I36"/>
-    <mergeCell ref="A88:B88"/>
-    <mergeCell ref="G88:I88"/>
-    <mergeCell ref="A43:I43"/>
-    <mergeCell ref="A44:I44"/>
-    <mergeCell ref="A45:I45"/>
-    <mergeCell ref="B83:D83"/>
-    <mergeCell ref="G83:I84"/>
-    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="G30:I31"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="A85:B85"/>
+    <mergeCell ref="G85:I85"/>
+    <mergeCell ref="A39:I39"/>
+    <mergeCell ref="A40:I40"/>
+    <mergeCell ref="A41:I41"/>
+    <mergeCell ref="B80:D80"/>
+    <mergeCell ref="G80:I81"/>
+    <mergeCell ref="B81:D81"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.19685039370078741" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="42" orientation="landscape" r:id="rId1"/>
+  <pageMargins left="0.59055118110236227" right="0.23622047244094491" top="0.39370078740157483" bottom="0.19685039370078741" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" scale="75" orientation="landscape" r:id="rId1"/>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="42" max="8" man="1"/>
+    <brk id="37" max="8" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:L31"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
@@ -2828,7 +2833,7 @@
     <col min="6" max="6" width="10.109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.44140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.33203125" customWidth="1"/>
-    <col min="9" max="9" width="28.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="18">
@@ -3357,7 +3362,16 @@
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.59055118110236227" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A5FE5A4-FC5F-4F48-8E89-D18467EAA6D7}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>